--- a/data/fmsForecastOutput/File1/RPT_RPT3404951962154TW_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT3404951962154TW_fmsForecastOutput.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="FMS Forecast Output" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMS Forecast Output" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1875,46 +1875,46 @@
         </is>
       </c>
       <c r="C8" s="148" t="n">
-        <v>428.7652043595864</v>
+        <v>428.7652043595863</v>
       </c>
       <c r="D8" s="149" t="n">
-        <v>462.8841290529318</v>
+        <v>462.8841290529316</v>
       </c>
       <c r="E8" s="149" t="n">
-        <v>496.7577484073837</v>
+        <v>496.7577484073834</v>
       </c>
       <c r="F8" s="149" t="n">
-        <v>527.401001525316</v>
+        <v>527.4010015253158</v>
       </c>
       <c r="G8" s="150" t="n">
         <v>570.2385414205852</v>
       </c>
       <c r="H8" s="148" t="n">
-        <v>27.85896398517191</v>
+        <v>27.8589639851719</v>
       </c>
       <c r="I8" s="149" t="n">
-        <v>32.5590755626007</v>
+        <v>32.55907556260069</v>
       </c>
       <c r="J8" s="149" t="n">
-        <v>37.73119500119178</v>
+        <v>37.73119500119176</v>
       </c>
       <c r="K8" s="149" t="n">
-        <v>43.74627003683111</v>
+        <v>43.74627003683108</v>
       </c>
       <c r="L8" s="150" t="n">
-        <v>50.66957115032589</v>
+        <v>50.66957115032588</v>
       </c>
       <c r="M8" s="151" t="n">
-        <v>6954726.807827573</v>
+        <v>6954726.807827571</v>
       </c>
       <c r="N8" s="152" t="n">
-        <v>8321350.402369337</v>
+        <v>8321350.402369333</v>
       </c>
       <c r="O8" s="152" t="n">
-        <v>9788535.20997492</v>
+        <v>9788535.209974915</v>
       </c>
       <c r="P8" s="152" t="n">
-        <v>11425440.70333798</v>
+        <v>11425440.70333797</v>
       </c>
       <c r="Q8" s="153" t="n">
         <v>13396108.17672268</v>
@@ -1925,46 +1925,46 @@
         </is>
       </c>
       <c r="T8" s="148" t="n">
-        <v>439.6693572641632</v>
+        <v>439.669357264163</v>
       </c>
       <c r="U8" s="149" t="n">
-        <v>474.6559782351289</v>
+        <v>474.6559782351287</v>
       </c>
       <c r="V8" s="149" t="n">
-        <v>509.391055378405</v>
+        <v>509.3910553784048</v>
       </c>
       <c r="W8" s="149" t="n">
-        <v>540.8136131462813</v>
+        <v>540.8136131462811</v>
       </c>
       <c r="X8" s="150" t="n">
-        <v>584.7405769974231</v>
+        <v>584.740576997423</v>
       </c>
       <c r="Y8" s="148" t="n">
         <v>34.17669179860263</v>
       </c>
       <c r="Z8" s="149" t="n">
-        <v>39.89772585879203</v>
+        <v>39.89772585879201</v>
       </c>
       <c r="AA8" s="149" t="n">
-        <v>46.18121951526273</v>
+        <v>46.1812195152627</v>
       </c>
       <c r="AB8" s="149" t="n">
-        <v>53.46506938446586</v>
+        <v>53.46506938446583</v>
       </c>
       <c r="AC8" s="150" t="n">
-        <v>61.85000092553748</v>
+        <v>61.85000092553746</v>
       </c>
       <c r="AD8" s="151" t="n">
-        <v>6954726.807827573</v>
+        <v>6954726.807827571</v>
       </c>
       <c r="AE8" s="152" t="n">
-        <v>8321350.402369337</v>
+        <v>8321350.402369333</v>
       </c>
       <c r="AF8" s="152" t="n">
-        <v>9788535.20997492</v>
+        <v>9788535.209974915</v>
       </c>
       <c r="AG8" s="152" t="n">
-        <v>11425440.70333798</v>
+        <v>11425440.70333797</v>
       </c>
       <c r="AH8" s="153" t="n">
         <v>13396108.17672268</v>
@@ -2022,10 +2022,10 @@
         </is>
       </c>
       <c r="C9" s="155" t="n">
-        <v>908.725553530213</v>
+        <v>908.7255535302129</v>
       </c>
       <c r="D9" s="156" t="n">
-        <v>993.578981144481</v>
+        <v>993.5789811444811</v>
       </c>
       <c r="E9" s="156" t="n">
         <v>1070.702405156692</v>
@@ -2049,22 +2049,22 @@
         <v>21.63402622883795</v>
       </c>
       <c r="L9" s="157" t="n">
-        <v>25.94072046430785</v>
+        <v>25.94072046430784</v>
       </c>
       <c r="M9" s="158" t="n">
-        <v>3105173.813214872</v>
+        <v>3105173.813214871</v>
       </c>
       <c r="N9" s="159" t="n">
-        <v>3875530.556646596</v>
+        <v>3875530.556646597</v>
       </c>
       <c r="O9" s="159" t="n">
-        <v>4716201.157766601</v>
+        <v>4716201.1577666</v>
       </c>
       <c r="P9" s="159" t="n">
         <v>5646648.175497905</v>
       </c>
       <c r="Q9" s="160" t="n">
-        <v>6803728.524562547</v>
+        <v>6803728.524562546</v>
       </c>
       <c r="S9" s="32" t="inlineStr">
         <is>
@@ -2072,19 +2072,19 @@
         </is>
       </c>
       <c r="T9" s="155" t="n">
-        <v>994.8598535110533</v>
+        <v>994.8598535110531</v>
       </c>
       <c r="U9" s="156" t="n">
-        <v>1087.756183143578</v>
+        <v>1087.756183143579</v>
       </c>
       <c r="V9" s="156" t="n">
-        <v>1172.189814416509</v>
+        <v>1172.189814416508</v>
       </c>
       <c r="W9" s="156" t="n">
         <v>1249.037985186783</v>
       </c>
       <c r="X9" s="157" t="n">
-        <v>1363.622236895819</v>
+        <v>1363.622236895818</v>
       </c>
       <c r="Y9" s="155" t="n">
         <v>12.86351186086133</v>
@@ -2093,7 +2093,7 @@
         <v>15.66125059862226</v>
       </c>
       <c r="AA9" s="156" t="n">
-        <v>18.77696095277867</v>
+        <v>18.77696095277866</v>
       </c>
       <c r="AB9" s="156" t="n">
         <v>22.39314037523445</v>
@@ -2102,19 +2102,19 @@
         <v>26.85373433006302</v>
       </c>
       <c r="AD9" s="158" t="n">
-        <v>3105173.813214872</v>
+        <v>3105173.813214871</v>
       </c>
       <c r="AE9" s="159" t="n">
-        <v>3875530.556646596</v>
+        <v>3875530.556646597</v>
       </c>
       <c r="AF9" s="159" t="n">
-        <v>4716201.157766601</v>
+        <v>4716201.1577666</v>
       </c>
       <c r="AG9" s="159" t="n">
         <v>5646648.175497905</v>
       </c>
       <c r="AH9" s="160" t="n">
-        <v>6803728.524562547</v>
+        <v>6803728.524562546</v>
       </c>
       <c r="AJ9" s="39" t="n"/>
       <c r="AQ9" s="40" t="inlineStr">
@@ -2173,16 +2173,16 @@
         <v>512.2820270682089</v>
       </c>
       <c r="D10" s="162" t="n">
-        <v>557.5015061140459</v>
+        <v>557.5015061140458</v>
       </c>
       <c r="E10" s="162" t="n">
-        <v>601.6161419840165</v>
+        <v>601.6161419840162</v>
       </c>
       <c r="F10" s="162" t="n">
-        <v>641.4949598732547</v>
+        <v>641.4949598732544</v>
       </c>
       <c r="G10" s="163" t="n">
-        <v>697.6407914031304</v>
+        <v>697.6407914031303</v>
       </c>
       <c r="H10" s="161" t="n">
         <v>20.14270816918894</v>
@@ -2191,13 +2191,13 @@
         <v>23.83754563762308</v>
       </c>
       <c r="J10" s="162" t="n">
-        <v>27.92692168446683</v>
+        <v>27.92692168446681</v>
       </c>
       <c r="K10" s="162" t="n">
-        <v>32.69369380069366</v>
+        <v>32.69369380069364</v>
       </c>
       <c r="L10" s="163" t="n">
-        <v>38.35449105650171</v>
+        <v>38.3544910565017</v>
       </c>
       <c r="M10" s="164" t="n">
         <v>10059900.62104245</v>
@@ -2209,7 +2209,7 @@
         <v>14504736.36774152</v>
       </c>
       <c r="P10" s="165" t="n">
-        <v>17072088.87883589</v>
+        <v>17072088.87883588</v>
       </c>
       <c r="Q10" s="166" t="n">
         <v>20199836.70128523</v>
@@ -2220,34 +2220,34 @@
         </is>
       </c>
       <c r="T10" s="161" t="n">
-        <v>531.1653512635378</v>
+        <v>531.1653512635377</v>
       </c>
       <c r="U10" s="162" t="n">
-        <v>578.2102640126875</v>
+        <v>578.2102640126873</v>
       </c>
       <c r="V10" s="162" t="n">
-        <v>624.1398513814325</v>
+        <v>624.1398513814323</v>
       </c>
       <c r="W10" s="162" t="n">
-        <v>665.6514271798305</v>
+        <v>665.6514271798302</v>
       </c>
       <c r="X10" s="163" t="n">
-        <v>724.0359344107221</v>
+        <v>724.035934410722</v>
       </c>
       <c r="Y10" s="161" t="n">
-        <v>22.61224950069323</v>
+        <v>22.61224950069322</v>
       </c>
       <c r="Z10" s="162" t="n">
-        <v>26.74596966688685</v>
+        <v>26.74596966688684</v>
       </c>
       <c r="AA10" s="162" t="n">
-        <v>31.31901277604872</v>
+        <v>31.31901277604871</v>
       </c>
       <c r="AB10" s="162" t="n">
-        <v>36.64648059641989</v>
+        <v>36.64648059641988</v>
       </c>
       <c r="AC10" s="163" t="n">
-        <v>42.9826981130621</v>
+        <v>42.98269811306209</v>
       </c>
       <c r="AD10" s="164" t="n">
         <v>10059900.62104245</v>
@@ -2259,7 +2259,7 @@
         <v>14504736.36774152</v>
       </c>
       <c r="AG10" s="165" t="n">
-        <v>17072088.87883589</v>
+        <v>17072088.87883588</v>
       </c>
       <c r="AH10" s="166" t="n">
         <v>20199836.70128523</v>
@@ -2327,7 +2327,7 @@
         <v>1341.362916536731</v>
       </c>
       <c r="F11" s="156" t="n">
-        <v>1408.858678459483</v>
+        <v>1408.858678459484</v>
       </c>
       <c r="G11" s="157" t="n">
         <v>1490.351452081349</v>
@@ -2339,10 +2339,10 @@
         <v>35.19968805467656</v>
       </c>
       <c r="J11" s="156" t="n">
-        <v>42.69992522632327</v>
+        <v>42.69992522632328</v>
       </c>
       <c r="K11" s="156" t="n">
-        <v>51.41590907964217</v>
+        <v>51.41590907964218</v>
       </c>
       <c r="L11" s="157" t="n">
         <v>62.32076619597447</v>
@@ -2389,10 +2389,10 @@
         <v>35.78284291459333</v>
       </c>
       <c r="AA11" s="156" t="n">
-        <v>43.41724002015321</v>
+        <v>43.41724002015322</v>
       </c>
       <c r="AB11" s="156" t="n">
-        <v>52.29412392064805</v>
+        <v>52.29412392064806</v>
       </c>
       <c r="AC11" s="157" t="n">
         <v>63.40529101218925</v>
@@ -2461,19 +2461,19 @@
         </is>
       </c>
       <c r="C12" s="161" t="n">
-        <v>515.494394687195</v>
+        <v>515.4943946871949</v>
       </c>
       <c r="D12" s="162" t="n">
-        <v>561.0764454942713</v>
+        <v>561.0764454942712</v>
       </c>
       <c r="E12" s="162" t="n">
-        <v>605.5625449721535</v>
+        <v>605.5625449721533</v>
       </c>
       <c r="F12" s="162" t="n">
-        <v>645.7674607822191</v>
+        <v>645.767460782219</v>
       </c>
       <c r="G12" s="163" t="n">
-        <v>702.317837759054</v>
+        <v>702.3178377590539</v>
       </c>
       <c r="H12" s="161" t="n">
         <v>20.21208884673394</v>
@@ -2482,19 +2482,19 @@
         <v>23.92594677188194</v>
       </c>
       <c r="J12" s="162" t="n">
-        <v>28.04156522239055</v>
+        <v>28.04156522239053</v>
       </c>
       <c r="K12" s="162" t="n">
         <v>32.83894545722222</v>
       </c>
       <c r="L12" s="163" t="n">
-        <v>38.54005434105279</v>
+        <v>38.54005434105278</v>
       </c>
       <c r="M12" s="164" t="n">
         <v>10173834.65969527</v>
       </c>
       <c r="N12" s="165" t="n">
-        <v>12338107.34176341</v>
+        <v>12338107.3417634</v>
       </c>
       <c r="O12" s="165" t="n">
         <v>14678187.87712436</v>
@@ -2511,40 +2511,40 @@
         </is>
       </c>
       <c r="T12" s="161" t="n">
-        <v>534.6001158672607</v>
+        <v>534.6001158672606</v>
       </c>
       <c r="U12" s="162" t="n">
-        <v>582.032895023043</v>
+        <v>582.0328950230428</v>
       </c>
       <c r="V12" s="162" t="n">
-        <v>628.3626608724381</v>
+        <v>628.3626608724378</v>
       </c>
       <c r="W12" s="162" t="n">
-        <v>670.2272849865598</v>
+        <v>670.2272849865594</v>
       </c>
       <c r="X12" s="163" t="n">
-        <v>729.0534484421622</v>
+        <v>729.0534484421621</v>
       </c>
       <c r="Y12" s="161" t="n">
         <v>22.67167478364848</v>
       </c>
       <c r="Z12" s="162" t="n">
-        <v>26.82350974660265</v>
+        <v>26.82350974660264</v>
       </c>
       <c r="AA12" s="162" t="n">
-        <v>31.42248067595709</v>
+        <v>31.42248067595707</v>
       </c>
       <c r="AB12" s="162" t="n">
-        <v>36.78016535612092</v>
+        <v>36.7801653561209</v>
       </c>
       <c r="AC12" s="163" t="n">
-        <v>43.15673686148604</v>
+        <v>43.15673686148603</v>
       </c>
       <c r="AD12" s="164" t="n">
         <v>10173834.65969527</v>
       </c>
       <c r="AE12" s="165" t="n">
-        <v>12338107.34176341</v>
+        <v>12338107.3417634</v>
       </c>
       <c r="AF12" s="165" t="n">
         <v>14678187.87712436</v>
@@ -2603,46 +2603,46 @@
         </is>
       </c>
       <c r="C13" s="155" t="n">
-        <v>941.0707137106635</v>
+        <v>941.0707137106632</v>
       </c>
       <c r="D13" s="156" t="n">
-        <v>972.6762582098899</v>
+        <v>972.6762582098897</v>
       </c>
       <c r="E13" s="156" t="n">
-        <v>851.4522878433247</v>
+        <v>851.4522878433245</v>
       </c>
       <c r="F13" s="156" t="n">
-        <v>879.7859300354993</v>
+        <v>879.7859300354991</v>
       </c>
       <c r="G13" s="157" t="n">
-        <v>918.1017327772662</v>
+        <v>918.101732777266</v>
       </c>
       <c r="H13" s="155" t="n">
-        <v>814.9086220666812</v>
+        <v>814.908622066681</v>
       </c>
       <c r="I13" s="156" t="n">
-        <v>849.1170384295579</v>
+        <v>849.1170384295576</v>
       </c>
       <c r="J13" s="156" t="n">
-        <v>744.7109307772943</v>
+        <v>744.7109307772942</v>
       </c>
       <c r="K13" s="156" t="n">
-        <v>775.5475039998214</v>
+        <v>775.5475039998212</v>
       </c>
       <c r="L13" s="157" t="n">
-        <v>817.3817675984617</v>
+        <v>817.3817675984616</v>
       </c>
       <c r="M13" s="158" t="n">
-        <v>7093576.675913888</v>
+        <v>7093576.675913887</v>
       </c>
       <c r="N13" s="159" t="n">
-        <v>8359337.200900509</v>
+        <v>8359337.200900506</v>
       </c>
       <c r="O13" s="159" t="n">
-        <v>8313683.433522604</v>
+        <v>8313683.433522603</v>
       </c>
       <c r="P13" s="159" t="n">
-        <v>9791972.644406566</v>
+        <v>9791972.644406565</v>
       </c>
       <c r="Q13" s="160" t="n">
         <v>11709892.56304629</v>
@@ -2653,46 +2653,46 @@
         </is>
       </c>
       <c r="T13" s="155" t="n">
-        <v>599.0591769772504</v>
+        <v>599.0591769772502</v>
       </c>
       <c r="U13" s="156" t="n">
-        <v>619.1783786480461</v>
+        <v>619.1783786480459</v>
       </c>
       <c r="V13" s="156" t="n">
-        <v>542.0106048987542</v>
+        <v>542.0106048987541</v>
       </c>
       <c r="W13" s="156" t="n">
         <v>560.0470054849385</v>
       </c>
       <c r="X13" s="157" t="n">
-        <v>584.4377690283068</v>
+        <v>584.4377690283067</v>
       </c>
       <c r="Y13" s="155" t="n">
-        <v>522.9816767319858</v>
+        <v>522.9816767319857</v>
       </c>
       <c r="Z13" s="156" t="n">
-        <v>544.7023298411501</v>
+        <v>544.70232984115</v>
       </c>
       <c r="AA13" s="156" t="n">
-        <v>477.6781451960846</v>
+        <v>477.6781451960845</v>
       </c>
       <c r="AB13" s="156" t="n">
-        <v>497.2493463976077</v>
+        <v>497.2493463976076</v>
       </c>
       <c r="AC13" s="157" t="n">
         <v>523.7921542433139</v>
       </c>
       <c r="AD13" s="158" t="n">
-        <v>7093576.675913888</v>
+        <v>7093576.675913887</v>
       </c>
       <c r="AE13" s="159" t="n">
-        <v>8359337.200900509</v>
+        <v>8359337.200900506</v>
       </c>
       <c r="AF13" s="159" t="n">
-        <v>8313683.433522604</v>
+        <v>8313683.433522603</v>
       </c>
       <c r="AG13" s="159" t="n">
-        <v>9791972.644406566</v>
+        <v>9791972.644406565</v>
       </c>
       <c r="AH13" s="160" t="n">
         <v>11709892.56304629</v>
@@ -2746,19 +2746,19 @@
         </is>
       </c>
       <c r="C14" s="167" t="n">
-        <v>633.1124791772467</v>
+        <v>633.1124791772464</v>
       </c>
       <c r="D14" s="168" t="n">
-        <v>676.7359147459596</v>
+        <v>676.7359147459595</v>
       </c>
       <c r="E14" s="168" t="n">
-        <v>676.1708350321177</v>
+        <v>676.1708350321173</v>
       </c>
       <c r="F14" s="168" t="n">
-        <v>714.5054165029691</v>
+        <v>714.505416502969</v>
       </c>
       <c r="G14" s="169" t="n">
-        <v>768.0330827235583</v>
+        <v>768.0330827235582</v>
       </c>
       <c r="H14" s="167" t="n">
         <v>33.72154689645549</v>
@@ -2767,25 +2767,25 @@
         <v>39.38441695345504</v>
       </c>
       <c r="J14" s="168" t="n">
-        <v>43.00700455683517</v>
+        <v>43.00700455683516</v>
       </c>
       <c r="K14" s="168" t="n">
-        <v>50.24012572746951</v>
+        <v>50.2401257274695</v>
       </c>
       <c r="L14" s="169" t="n">
         <v>59.00936239108594</v>
       </c>
       <c r="M14" s="170" t="n">
-        <v>17267411.33560916</v>
+        <v>17267411.33560915</v>
       </c>
       <c r="N14" s="171" t="n">
         <v>20697444.54266391</v>
       </c>
       <c r="O14" s="171" t="n">
-        <v>22991871.31064697</v>
+        <v>22991871.31064696</v>
       </c>
       <c r="P14" s="171" t="n">
-        <v>27073987.67978462</v>
+        <v>27073987.67978461</v>
       </c>
       <c r="Q14" s="172" t="n">
         <v>32165842.26166061</v>
@@ -2796,46 +2796,46 @@
         </is>
       </c>
       <c r="T14" s="167" t="n">
-        <v>559.3239426982653</v>
+        <v>559.3239426982652</v>
       </c>
       <c r="U14" s="168" t="n">
-        <v>596.4854696273477</v>
+        <v>596.4854696273476</v>
       </c>
       <c r="V14" s="168" t="n">
-        <v>594.1355977485341</v>
+        <v>594.135597748534</v>
       </c>
       <c r="W14" s="168" t="n">
-        <v>625.7060015490484</v>
+        <v>625.7060015490483</v>
       </c>
       <c r="X14" s="169" t="n">
-        <v>668.806433637718</v>
+        <v>668.8064336377179</v>
       </c>
       <c r="Y14" s="167" t="n">
-        <v>37.35026978389495</v>
+        <v>37.35026978389494</v>
       </c>
       <c r="Z14" s="168" t="n">
-        <v>43.54420924544761</v>
+        <v>43.5442092454476</v>
       </c>
       <c r="AA14" s="168" t="n">
-        <v>47.45208672263794</v>
+        <v>47.45208672263792</v>
       </c>
       <c r="AB14" s="168" t="n">
-        <v>55.30207356751717</v>
+        <v>55.30207356751716</v>
       </c>
       <c r="AC14" s="169" t="n">
         <v>64.80501651495628</v>
       </c>
       <c r="AD14" s="170" t="n">
-        <v>17267411.33560916</v>
+        <v>17267411.33560915</v>
       </c>
       <c r="AE14" s="171" t="n">
         <v>20697444.54266391</v>
       </c>
       <c r="AF14" s="171" t="n">
-        <v>22991871.31064697</v>
+        <v>22991871.31064696</v>
       </c>
       <c r="AG14" s="171" t="n">
-        <v>27073987.67978462</v>
+        <v>27073987.67978461</v>
       </c>
       <c r="AH14" s="172" t="n">
         <v>32165842.26166061</v>
@@ -3870,7 +3870,7 @@
         <v>1571.638735760075</v>
       </c>
       <c r="M24" s="79" t="n">
-        <v>8704.751040581632</v>
+        <v>8704.751040581634</v>
       </c>
       <c r="N24" s="80" t="n">
         <v>9844.740857351189</v>
@@ -3920,7 +3920,7 @@
         <v>2319.824070106877</v>
       </c>
       <c r="AD24" s="79" t="n">
-        <v>13563.71932615367</v>
+        <v>13563.71932615368</v>
       </c>
       <c r="AE24" s="80" t="n">
         <v>15346.61546855934</v>
@@ -3948,7 +3948,7 @@
         <v>30584.22656707017</v>
       </c>
       <c r="E25" s="92" t="n">
-        <v>34003.05088514335</v>
+        <v>34003.05088514336</v>
       </c>
       <c r="F25" s="92" t="n">
         <v>37891.92783491252</v>
@@ -4408,40 +4408,40 @@
         </is>
       </c>
       <c r="C35" s="148" t="n">
-        <v>440.0611871384052</v>
+        <v>440.0611871384051</v>
       </c>
       <c r="D35" s="149" t="n">
-        <v>486.316452135398</v>
+        <v>486.3164521353978</v>
       </c>
       <c r="E35" s="149" t="n">
-        <v>525.3022317924052</v>
+        <v>525.3022317924049</v>
       </c>
       <c r="F35" s="149" t="n">
-        <v>564.8161694201508</v>
+        <v>564.8161694201506</v>
       </c>
       <c r="G35" s="150" t="n">
-        <v>612.3950144274173</v>
+        <v>612.3950144274172</v>
       </c>
       <c r="H35" s="148" t="n">
         <v>28.59291901280124</v>
       </c>
       <c r="I35" s="149" t="n">
-        <v>34.20729534367263</v>
+        <v>34.20729534367261</v>
       </c>
       <c r="J35" s="149" t="n">
-        <v>39.8992889509318</v>
+        <v>39.89928895093178</v>
       </c>
       <c r="K35" s="149" t="n">
-        <v>46.84974165229456</v>
+        <v>46.84974165229454</v>
       </c>
       <c r="L35" s="150" t="n">
         <v>54.41546037616656</v>
       </c>
       <c r="M35" s="151" t="n">
-        <v>7137951.7371218</v>
+        <v>7137951.737121798</v>
       </c>
       <c r="N35" s="152" t="n">
-        <v>8742597.446439909</v>
+        <v>8742597.446439905</v>
       </c>
       <c r="O35" s="152" t="n">
         <v>10350999.87521792</v>
@@ -4458,40 +4458,40 @@
         </is>
       </c>
       <c r="T35" s="148" t="n">
-        <v>451.2526141085436</v>
+        <v>451.2526141085434</v>
       </c>
       <c r="U35" s="149" t="n">
-        <v>498.6842210219057</v>
+        <v>498.6842210219056</v>
       </c>
       <c r="V35" s="149" t="n">
-        <v>538.6614684989734</v>
+        <v>538.661468498973</v>
       </c>
       <c r="W35" s="149" t="n">
-        <v>579.1803058092817</v>
+        <v>579.1803058092814</v>
       </c>
       <c r="X35" s="150" t="n">
-        <v>627.9691533907013</v>
+        <v>627.9691533907012</v>
       </c>
       <c r="Y35" s="148" t="n">
-        <v>35.07708977415814</v>
+        <v>35.07708977415813</v>
       </c>
       <c r="Z35" s="149" t="n">
-        <v>41.91744600882546</v>
+        <v>41.91744600882544</v>
       </c>
       <c r="AA35" s="149" t="n">
-        <v>48.83486519543519</v>
+        <v>48.83486519543516</v>
       </c>
       <c r="AB35" s="149" t="n">
-        <v>57.25801733440024</v>
+        <v>57.25801733440021</v>
       </c>
       <c r="AC35" s="150" t="n">
-        <v>66.42243457408468</v>
+        <v>66.42243457408466</v>
       </c>
       <c r="AD35" s="151" t="n">
-        <v>7137951.7371218</v>
+        <v>7137951.737121798</v>
       </c>
       <c r="AE35" s="152" t="n">
-        <v>8742597.446439909</v>
+        <v>8742597.446439905</v>
       </c>
       <c r="AF35" s="152" t="n">
         <v>10350999.87521792</v>
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="C36" s="155" t="n">
-        <v>933.3459519124846</v>
+        <v>933.3459519124845</v>
       </c>
       <c r="D36" s="156" t="n">
         <v>1044.503135592479</v>
@@ -4537,22 +4537,22 @@
         <v>23.17526677814017</v>
       </c>
       <c r="L36" s="157" t="n">
-        <v>27.85909935109128</v>
+        <v>27.85909935109127</v>
       </c>
       <c r="M36" s="158" t="n">
-        <v>3189303.302069403</v>
+        <v>3189303.302069402</v>
       </c>
       <c r="N36" s="159" t="n">
-        <v>4074164.103027856</v>
+        <v>4074164.103027857</v>
       </c>
       <c r="O36" s="159" t="n">
-        <v>4989240.268658337</v>
+        <v>4989240.268658336</v>
       </c>
       <c r="P36" s="159" t="n">
         <v>6048923.879690218</v>
       </c>
       <c r="Q36" s="160" t="n">
-        <v>7306880.669888872</v>
+        <v>7306880.669888871</v>
       </c>
       <c r="S36" s="32" t="inlineStr">
         <is>
@@ -4563,16 +4563,16 @@
         <v>1021.813916630349</v>
       </c>
       <c r="U36" s="156" t="n">
-        <v>1143.507225509996</v>
+        <v>1143.507225509997</v>
       </c>
       <c r="V36" s="156" t="n">
-        <v>1240.052412727773</v>
+        <v>1240.052412727772</v>
       </c>
       <c r="W36" s="156" t="n">
         <v>1338.02132883377</v>
       </c>
       <c r="X36" s="157" t="n">
-        <v>1464.465392443817</v>
+        <v>1464.465392443816</v>
       </c>
       <c r="Y36" s="155" t="n">
         <v>13.21202719134714</v>
@@ -4581,7 +4581,7 @@
         <v>16.46394063078697</v>
       </c>
       <c r="AA36" s="156" t="n">
-        <v>19.8640317863356</v>
+        <v>19.86403178633559</v>
       </c>
       <c r="AB36" s="156" t="n">
         <v>23.98846135744359</v>
@@ -4590,19 +4590,19 @@
         <v>28.83963279579628</v>
       </c>
       <c r="AD36" s="158" t="n">
-        <v>3189303.302069403</v>
+        <v>3189303.302069402</v>
       </c>
       <c r="AE36" s="159" t="n">
-        <v>4074164.103027856</v>
+        <v>4074164.103027857</v>
       </c>
       <c r="AF36" s="159" t="n">
-        <v>4989240.268658337</v>
+        <v>4989240.268658336</v>
       </c>
       <c r="AG36" s="159" t="n">
         <v>6048923.879690218</v>
       </c>
       <c r="AH36" s="160" t="n">
-        <v>7306880.669888872</v>
+        <v>7306880.669888871</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" thickTop="1">
@@ -4612,19 +4612,19 @@
         </is>
       </c>
       <c r="C37" s="161" t="n">
-        <v>525.8965614889968</v>
+        <v>525.8965614889967</v>
       </c>
       <c r="D37" s="162" t="n">
-        <v>585.8353370294247</v>
+        <v>585.8353370294246</v>
       </c>
       <c r="E37" s="162" t="n">
-        <v>636.2705159531399</v>
+        <v>636.2705159531396</v>
       </c>
       <c r="F37" s="162" t="n">
-        <v>687.0676757149433</v>
+        <v>687.067675714943</v>
       </c>
       <c r="G37" s="163" t="n">
-        <v>749.2216176304973</v>
+        <v>749.2216176304971</v>
       </c>
       <c r="H37" s="161" t="n">
         <v>20.67802578567208</v>
@@ -4633,13 +4633,13 @@
         <v>25.04903830648032</v>
       </c>
       <c r="J37" s="162" t="n">
-        <v>29.53557198541843</v>
+        <v>29.53557198541842</v>
       </c>
       <c r="K37" s="162" t="n">
-        <v>35.01630038467768</v>
+        <v>35.01630038467766</v>
       </c>
       <c r="L37" s="163" t="n">
-        <v>41.19027182305571</v>
+        <v>41.1902718230557</v>
       </c>
       <c r="M37" s="164" t="n">
         <v>10327255.0391912</v>
@@ -4648,13 +4648,13 @@
         <v>12816761.54946776</v>
       </c>
       <c r="O37" s="165" t="n">
-        <v>15340240.14387626</v>
+        <v>15340240.14387625</v>
       </c>
       <c r="P37" s="165" t="n">
-        <v>18284914.39418048</v>
+        <v>18284914.39418047</v>
       </c>
       <c r="Q37" s="166" t="n">
-        <v>21693333.46860386</v>
+        <v>21693333.46860385</v>
       </c>
       <c r="S37" s="42" t="inlineStr">
         <is>
@@ -4662,34 +4662,34 @@
         </is>
       </c>
       <c r="T37" s="161" t="n">
-        <v>545.2817335994429</v>
+        <v>545.2817335994428</v>
       </c>
       <c r="U37" s="162" t="n">
-        <v>607.596573600021</v>
+        <v>607.5965736000207</v>
       </c>
       <c r="V37" s="162" t="n">
-        <v>660.091639090247</v>
+        <v>660.0916390902468</v>
       </c>
       <c r="W37" s="162" t="n">
-        <v>712.9402528729811</v>
+        <v>712.9402528729807</v>
       </c>
       <c r="X37" s="163" t="n">
-        <v>777.5683140757585</v>
+        <v>777.5683140757584</v>
       </c>
       <c r="Y37" s="161" t="n">
-        <v>23.21319826112601</v>
+        <v>23.213198261126</v>
       </c>
       <c r="Z37" s="162" t="n">
         <v>28.1052768147574</v>
       </c>
       <c r="AA37" s="162" t="n">
-        <v>33.12305476452612</v>
+        <v>33.1230547645261</v>
       </c>
       <c r="AB37" s="162" t="n">
-        <v>39.24989878562682</v>
+        <v>39.2498987856268</v>
       </c>
       <c r="AC37" s="163" t="n">
-        <v>46.16067037253122</v>
+        <v>46.16067037253121</v>
       </c>
       <c r="AD37" s="164" t="n">
         <v>10327255.0391912</v>
@@ -4698,13 +4698,13 @@
         <v>12816761.54946776</v>
       </c>
       <c r="AF37" s="165" t="n">
-        <v>15340240.14387626</v>
+        <v>15340240.14387625</v>
       </c>
       <c r="AG37" s="165" t="n">
-        <v>18284914.39418048</v>
+        <v>18284914.39418047</v>
       </c>
       <c r="AH37" s="166" t="n">
-        <v>21693333.46860386</v>
+        <v>21693333.46860385</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" thickBot="1">
@@ -4738,7 +4738,7 @@
         <v>45.05127868864555</v>
       </c>
       <c r="K38" s="156" t="n">
-        <v>54.92835353604725</v>
+        <v>54.92835353604726</v>
       </c>
       <c r="L38" s="157" t="n">
         <v>66.74508846172439</v>
@@ -4753,7 +4753,7 @@
         <v>183002.9501633727</v>
       </c>
       <c r="P38" s="159" t="n">
-        <v>224267.1256702032</v>
+        <v>224267.1256702033</v>
       </c>
       <c r="Q38" s="160" t="n">
         <v>274295.1620519693</v>
@@ -4764,13 +4764,13 @@
         </is>
       </c>
       <c r="T38" s="155" t="n">
-        <v>1276.747016565602</v>
+        <v>1276.747016565603</v>
       </c>
       <c r="U38" s="156" t="n">
         <v>1422.643443339115</v>
       </c>
       <c r="V38" s="156" t="n">
-        <v>1526.811522021489</v>
+        <v>1526.81152202149</v>
       </c>
       <c r="W38" s="156" t="n">
         <v>1623.774135778494</v>
@@ -4785,10 +4785,10 @@
         <v>37.52459740273842</v>
       </c>
       <c r="AA38" s="156" t="n">
-        <v>45.80809380045279</v>
+        <v>45.8080938004528</v>
       </c>
       <c r="AB38" s="156" t="n">
-        <v>55.86656305389617</v>
+        <v>55.86656305389618</v>
       </c>
       <c r="AC38" s="157" t="n">
         <v>67.90660667171498</v>
@@ -4803,7 +4803,7 @@
         <v>183002.9501633727</v>
       </c>
       <c r="AG38" s="159" t="n">
-        <v>224267.1256702032</v>
+        <v>224267.1256702033</v>
       </c>
       <c r="AH38" s="160" t="n">
         <v>274295.1620519693</v>
@@ -4816,34 +4816,34 @@
         </is>
       </c>
       <c r="C39" s="161" t="n">
-        <v>529.1831233003485</v>
+        <v>529.1831233003484</v>
       </c>
       <c r="D39" s="162" t="n">
-        <v>589.5781752582209</v>
+        <v>589.5781752582208</v>
       </c>
       <c r="E39" s="162" t="n">
-        <v>640.4260984353664</v>
+        <v>640.426098435366</v>
       </c>
       <c r="F39" s="162" t="n">
-        <v>691.6223094797049</v>
+        <v>691.6223094797047</v>
       </c>
       <c r="G39" s="163" t="n">
-        <v>754.2185851982805</v>
+        <v>754.2185851982804</v>
       </c>
       <c r="H39" s="161" t="n">
-        <v>20.74881204252306</v>
+        <v>20.74881204252305</v>
       </c>
       <c r="I39" s="162" t="n">
-        <v>25.14134420072622</v>
+        <v>25.14134420072621</v>
       </c>
       <c r="J39" s="162" t="n">
-        <v>29.65597915277644</v>
+        <v>29.65597915277643</v>
       </c>
       <c r="K39" s="162" t="n">
-        <v>35.1707831027764</v>
+        <v>35.17078310277639</v>
       </c>
       <c r="L39" s="163" t="n">
-        <v>41.38813468175927</v>
+        <v>41.38813468175926</v>
       </c>
       <c r="M39" s="164" t="n">
         <v>10443996.39772187</v>
@@ -4858,7 +4858,7 @@
         <v>18509181.51985068</v>
       </c>
       <c r="Q39" s="166" t="n">
-        <v>21967628.63065583</v>
+        <v>21967628.63065582</v>
       </c>
       <c r="S39" s="42" t="inlineStr">
         <is>
@@ -4866,34 +4866,34 @@
         </is>
       </c>
       <c r="T39" s="161" t="n">
-        <v>548.7961885657969</v>
+        <v>548.7961885657968</v>
       </c>
       <c r="U39" s="162" t="n">
-        <v>611.5991768031706</v>
+        <v>611.5991768031704</v>
       </c>
       <c r="V39" s="162" t="n">
-        <v>664.5388666227793</v>
+        <v>664.538866622779</v>
       </c>
       <c r="W39" s="162" t="n">
-        <v>717.8189841854606</v>
+        <v>717.8189841854603</v>
       </c>
       <c r="X39" s="163" t="n">
-        <v>782.9299369249667</v>
+        <v>782.9299369249666</v>
       </c>
       <c r="Y39" s="161" t="n">
         <v>23.27371121026639</v>
       </c>
       <c r="Z39" s="162" t="n">
-        <v>28.18609844954641</v>
+        <v>28.1860984495464</v>
       </c>
       <c r="AA39" s="162" t="n">
-        <v>33.23154126612846</v>
+        <v>33.23154126612844</v>
       </c>
       <c r="AB39" s="162" t="n">
-        <v>39.3918623212026</v>
+        <v>39.39186232120258</v>
       </c>
       <c r="AC39" s="163" t="n">
-        <v>46.34598648569619</v>
+        <v>46.34598648569618</v>
       </c>
       <c r="AD39" s="164" t="n">
         <v>10443996.39772187</v>
@@ -4908,7 +4908,7 @@
         <v>18509181.51985068</v>
       </c>
       <c r="AH39" s="166" t="n">
-        <v>21967628.63065583</v>
+        <v>21967628.63065582</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" thickBot="1">
@@ -4918,46 +4918,46 @@
         </is>
       </c>
       <c r="C40" s="155" t="n">
-        <v>912.8088058909642</v>
+        <v>912.808805890964</v>
       </c>
       <c r="D40" s="156" t="n">
-        <v>950.0056564993657</v>
+        <v>950.0056564993655</v>
       </c>
       <c r="E40" s="156" t="n">
-        <v>883.1447112442968</v>
+        <v>883.1447112442966</v>
       </c>
       <c r="F40" s="156" t="n">
-        <v>923.1987952775479</v>
+        <v>923.1987952775477</v>
       </c>
       <c r="G40" s="157" t="n">
-        <v>965.0869980434799</v>
+        <v>965.0869980434796</v>
       </c>
       <c r="H40" s="155" t="n">
-        <v>790.4355702303156</v>
+        <v>790.4355702303154</v>
       </c>
       <c r="I40" s="156" t="n">
-        <v>829.3262868599821</v>
+        <v>829.3262868599819</v>
       </c>
       <c r="J40" s="156" t="n">
-        <v>772.4302692141051</v>
+        <v>772.430269214105</v>
       </c>
       <c r="K40" s="156" t="n">
-        <v>813.8167444258338</v>
+        <v>813.8167444258336</v>
       </c>
       <c r="L40" s="157" t="n">
-        <v>859.2125340628764</v>
+        <v>859.2125340628763</v>
       </c>
       <c r="M40" s="158" t="n">
-        <v>6880544.852475076</v>
+        <v>6880544.852475075</v>
       </c>
       <c r="N40" s="159" t="n">
-        <v>8164502.380325819</v>
+        <v>8164502.380325817</v>
       </c>
       <c r="O40" s="159" t="n">
-        <v>8623132.100416467</v>
+        <v>8623132.100416465</v>
       </c>
       <c r="P40" s="159" t="n">
-        <v>10275155.62603063</v>
+        <v>10275155.62603062</v>
       </c>
       <c r="Q40" s="160" t="n">
         <v>12309164.28716041</v>
@@ -4968,46 +4968,46 @@
         </is>
       </c>
       <c r="T40" s="155" t="n">
-        <v>581.0684404772074</v>
+        <v>581.0684404772072</v>
       </c>
       <c r="U40" s="156" t="n">
-        <v>604.7469105294226</v>
+        <v>604.7469105294224</v>
       </c>
       <c r="V40" s="156" t="n">
-        <v>562.1851112375393</v>
+        <v>562.1851112375392</v>
       </c>
       <c r="W40" s="156" t="n">
-        <v>587.6824158140734</v>
+        <v>587.6824158140732</v>
       </c>
       <c r="X40" s="157" t="n">
-        <v>614.3472688462871</v>
+        <v>614.347268846287</v>
       </c>
       <c r="Y40" s="155" t="n">
-        <v>507.2756732150859</v>
+        <v>507.2756732150858</v>
       </c>
       <c r="Z40" s="156" t="n">
-        <v>532.0067083880781</v>
+        <v>532.006708388078</v>
       </c>
       <c r="AA40" s="156" t="n">
-        <v>495.4580939296666</v>
+        <v>495.4580939296665</v>
       </c>
       <c r="AB40" s="156" t="n">
-        <v>521.7860184787185</v>
+        <v>521.7860184787183</v>
       </c>
       <c r="AC40" s="157" t="n">
         <v>550.5980216465226</v>
       </c>
       <c r="AD40" s="158" t="n">
-        <v>6880544.852475076</v>
+        <v>6880544.852475075</v>
       </c>
       <c r="AE40" s="159" t="n">
-        <v>8164502.380325819</v>
+        <v>8164502.380325817</v>
       </c>
       <c r="AF40" s="159" t="n">
-        <v>8623132.100416467</v>
+        <v>8623132.100416465</v>
       </c>
       <c r="AG40" s="159" t="n">
-        <v>10275155.62603063</v>
+        <v>10275155.62603062</v>
       </c>
       <c r="AH40" s="160" t="n">
         <v>12309164.28716041</v>
@@ -5020,16 +5020,16 @@
         </is>
       </c>
       <c r="C41" s="179" t="n">
-        <v>635.2071569003208</v>
+        <v>635.2071569003207</v>
       </c>
       <c r="D41" s="180" t="n">
-        <v>690.8582290780603</v>
+        <v>690.85822907806</v>
       </c>
       <c r="E41" s="180" t="n">
-        <v>710.1237849514898</v>
+        <v>710.1237849514895</v>
       </c>
       <c r="F41" s="180" t="n">
-        <v>759.6429844184454</v>
+        <v>759.6429844184451</v>
       </c>
       <c r="G41" s="181" t="n">
         <v>818.4368597095871</v>
@@ -5038,13 +5038,13 @@
         <v>33.83311597050596</v>
       </c>
       <c r="I41" s="180" t="n">
-        <v>40.20630198110575</v>
+        <v>40.20630198110574</v>
       </c>
       <c r="J41" s="180" t="n">
-        <v>45.16653968649079</v>
+        <v>45.16653968649078</v>
       </c>
       <c r="K41" s="180" t="n">
-        <v>53.4139534336396</v>
+        <v>53.41395343363958</v>
       </c>
       <c r="L41" s="181" t="n">
         <v>62.88197518466609</v>
@@ -5056,10 +5056,10 @@
         <v>21129364.60384826</v>
       </c>
       <c r="O41" s="183" t="n">
-        <v>24146375.1944561</v>
+        <v>24146375.19445609</v>
       </c>
       <c r="P41" s="183" t="n">
-        <v>28784337.14588131</v>
+        <v>28784337.1458813</v>
       </c>
       <c r="Q41" s="184" t="n">
         <v>34276792.91781624</v>
@@ -5070,16 +5070,16 @@
         </is>
       </c>
       <c r="T41" s="185" t="n">
-        <v>561.1744881246873</v>
+        <v>561.1744881246871</v>
       </c>
       <c r="U41" s="186" t="n">
-        <v>608.9330952270179</v>
+        <v>608.9330952270177</v>
       </c>
       <c r="V41" s="186" t="n">
-        <v>623.9692657367639</v>
+        <v>623.9692657367636</v>
       </c>
       <c r="W41" s="186" t="n">
-        <v>665.233829453099</v>
+        <v>665.2338294530988</v>
       </c>
       <c r="X41" s="187" t="n">
         <v>712.6982542977797</v>
@@ -5088,13 +5088,13 @@
         <v>37.47384463139883</v>
       </c>
       <c r="Z41" s="186" t="n">
-        <v>44.45290198201948</v>
+        <v>44.45290198201947</v>
       </c>
       <c r="AA41" s="186" t="n">
-        <v>49.83482528601727</v>
+        <v>49.83482528601726</v>
       </c>
       <c r="AB41" s="186" t="n">
-        <v>58.79568053517002</v>
+        <v>58.79568053517</v>
       </c>
       <c r="AC41" s="187" t="n">
         <v>69.05798122894045</v>
@@ -5106,10 +5106,10 @@
         <v>21129364.60384826</v>
       </c>
       <c r="AF41" s="189" t="n">
-        <v>24146375.1944561</v>
+        <v>24146375.19445609</v>
       </c>
       <c r="AG41" s="189" t="n">
-        <v>28784337.14588131</v>
+        <v>28784337.1458813</v>
       </c>
       <c r="AH41" s="190" t="n">
         <v>34276792.91781624</v>
@@ -6334,7 +6334,7 @@
         </is>
       </c>
       <c r="C57" s="148" t="n">
-        <v>0.3018039097730817</v>
+        <v>0.3018039097730816</v>
       </c>
       <c r="D57" s="149" t="n">
         <v>0.1903269611403116</v>
@@ -6343,40 +6343,40 @@
         <v>0.1360385649083278</v>
       </c>
       <c r="F57" s="149" t="n">
-        <v>0.08863977724435804</v>
+        <v>0.08863977724435801</v>
       </c>
       <c r="G57" s="150" t="n">
-        <v>0.04819396746469855</v>
+        <v>0.04819396746469854</v>
       </c>
       <c r="H57" s="148" t="n">
-        <v>0.01960967020518994</v>
+        <v>0.01960967020518993</v>
       </c>
       <c r="I57" s="149" t="n">
-        <v>0.01338751864758567</v>
+        <v>0.01338751864758566</v>
       </c>
       <c r="J57" s="149" t="n">
         <v>0.0103327983039914</v>
       </c>
       <c r="K57" s="149" t="n">
-        <v>0.007352393378324122</v>
+        <v>0.00735239337832412</v>
       </c>
       <c r="L57" s="150" t="n">
-        <v>0.004282361654099308</v>
+        <v>0.004282361654099307</v>
       </c>
       <c r="M57" s="151" t="n">
-        <v>4895.368655535111</v>
+        <v>4895.368655535109</v>
       </c>
       <c r="N57" s="152" t="n">
-        <v>3421.541667257201</v>
+        <v>3421.5416672572</v>
       </c>
       <c r="O57" s="152" t="n">
         <v>2680.61904779306</v>
       </c>
       <c r="P57" s="152" t="n">
-        <v>1920.262790426056</v>
+        <v>1920.262790426055</v>
       </c>
       <c r="Q57" s="153" t="n">
-        <v>1132.178123236286</v>
+        <v>1132.178123236285</v>
       </c>
       <c r="S57" s="21" t="inlineStr">
         <is>
@@ -6384,49 +6384,49 @@
         </is>
       </c>
       <c r="T57" s="148" t="n">
-        <v>0.3094792433726917</v>
+        <v>0.3094792433726916</v>
       </c>
       <c r="U57" s="149" t="n">
-        <v>0.1951672659622414</v>
+        <v>0.1951672659622413</v>
       </c>
       <c r="V57" s="149" t="n">
         <v>0.1394982330381034</v>
       </c>
       <c r="W57" s="149" t="n">
-        <v>0.09089402193276215</v>
+        <v>0.09089402193276214</v>
       </c>
       <c r="X57" s="150" t="n">
-        <v>0.04941961354084923</v>
+        <v>0.04941961354084921</v>
       </c>
       <c r="Y57" s="148" t="n">
-        <v>0.0240566610887516</v>
+        <v>0.02405666108875159</v>
       </c>
       <c r="Z57" s="149" t="n">
-        <v>0.01640499736867144</v>
+        <v>0.01640499736867143</v>
       </c>
       <c r="AA57" s="149" t="n">
         <v>0.0126468622758566</v>
       </c>
       <c r="AB57" s="149" t="n">
-        <v>0.008985822603459193</v>
+        <v>0.008985822603459192</v>
       </c>
       <c r="AC57" s="150" t="n">
         <v>0.005227280718120403</v>
       </c>
       <c r="AD57" s="151" t="n">
-        <v>4895.368655535111</v>
+        <v>4895.368655535109</v>
       </c>
       <c r="AE57" s="152" t="n">
-        <v>3421.541667257201</v>
+        <v>3421.5416672572</v>
       </c>
       <c r="AF57" s="152" t="n">
         <v>2680.61904779306</v>
       </c>
       <c r="AG57" s="152" t="n">
-        <v>1920.262790426056</v>
+        <v>1920.262790426055</v>
       </c>
       <c r="AH57" s="153" t="n">
-        <v>1132.178123236286</v>
+        <v>1132.178123236285</v>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" thickBot="1">
@@ -6436,10 +6436,10 @@
         </is>
       </c>
       <c r="C58" s="155" t="n">
-        <v>0.3314441535800955</v>
+        <v>0.3314441535800956</v>
       </c>
       <c r="D58" s="156" t="n">
-        <v>0.1490710963661512</v>
+        <v>0.1490710963661511</v>
       </c>
       <c r="E58" s="156" t="n">
         <v>0.1076583928418591</v>
@@ -6451,7 +6451,7 @@
         <v>0.03883501500445392</v>
       </c>
       <c r="H58" s="155" t="n">
-        <v>0.004534057475919487</v>
+        <v>0.004534057475919488</v>
       </c>
       <c r="I58" s="156" t="n">
         <v>0.002270543842409042</v>
@@ -6469,7 +6469,7 @@
         <v>1132.566045096764</v>
       </c>
       <c r="N58" s="159" t="n">
-        <v>581.4631750908766</v>
+        <v>581.4631750908765</v>
       </c>
       <c r="O58" s="159" t="n">
         <v>474.2107933247449</v>
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="T58" s="155" t="n">
-        <v>0.3628603606411359</v>
+        <v>0.362860360641136</v>
       </c>
       <c r="U58" s="156" t="n">
         <v>0.1632009230041207</v>
       </c>
       <c r="V58" s="156" t="n">
-        <v>0.1178628822704571</v>
+        <v>0.117862882270457</v>
       </c>
       <c r="W58" s="156" t="n">
         <v>0.0773791333719543</v>
@@ -6501,7 +6501,7 @@
         <v>0.04251602388459307</v>
       </c>
       <c r="Y58" s="155" t="n">
-        <v>0.004691774963549488</v>
+        <v>0.004691774963549489</v>
       </c>
       <c r="Z58" s="156" t="n">
         <v>0.002349727441408274</v>
@@ -6519,7 +6519,7 @@
         <v>1132.566045096764</v>
       </c>
       <c r="AE58" s="159" t="n">
-        <v>581.4631750908766</v>
+        <v>581.4631750908765</v>
       </c>
       <c r="AF58" s="159" t="n">
         <v>474.2107933247449</v>
@@ -6538,28 +6538,28 @@
         </is>
       </c>
       <c r="C59" s="161" t="n">
-        <v>0.3069615420469733</v>
+        <v>0.3069615420469732</v>
       </c>
       <c r="D59" s="162" t="n">
-        <v>0.1829714691887039</v>
+        <v>0.1829714691887038</v>
       </c>
       <c r="E59" s="162" t="n">
-        <v>0.1308535715168515</v>
+        <v>0.1308535715168514</v>
       </c>
       <c r="F59" s="162" t="n">
-        <v>0.0852996805615526</v>
+        <v>0.08529968056155257</v>
       </c>
       <c r="G59" s="163" t="n">
-        <v>0.04642836341778474</v>
+        <v>0.04642836341778473</v>
       </c>
       <c r="H59" s="161" t="n">
-        <v>0.01206959532818658</v>
+        <v>0.01206959532818657</v>
       </c>
       <c r="I59" s="162" t="n">
-        <v>0.007823460025373347</v>
+        <v>0.007823460025373345</v>
       </c>
       <c r="J59" s="162" t="n">
-        <v>0.006074201120722217</v>
+        <v>0.006074201120722216</v>
       </c>
       <c r="K59" s="162" t="n">
         <v>0.004347285344420132</v>
@@ -6568,16 +6568,16 @@
         <v>0.002552511652728805</v>
       </c>
       <c r="M59" s="164" t="n">
-        <v>6027.934700631875</v>
+        <v>6027.934700631873</v>
       </c>
       <c r="N59" s="165" t="n">
-        <v>4003.004842348078</v>
+        <v>4003.004842348077</v>
       </c>
       <c r="O59" s="165" t="n">
-        <v>3154.829841117805</v>
+        <v>3154.829841117804</v>
       </c>
       <c r="P59" s="165" t="n">
-        <v>2270.078206336738</v>
+        <v>2270.078206336737</v>
       </c>
       <c r="Q59" s="166" t="n">
         <v>1344.309809437798</v>
@@ -6588,46 +6588,46 @@
         </is>
       </c>
       <c r="T59" s="161" t="n">
-        <v>0.3182765092089958</v>
+        <v>0.3182765092089957</v>
       </c>
       <c r="U59" s="162" t="n">
-        <v>0.1897680640251894</v>
+        <v>0.1897680640251893</v>
       </c>
       <c r="V59" s="162" t="n">
         <v>0.1357525554582396</v>
       </c>
       <c r="W59" s="162" t="n">
-        <v>0.0885117696248145</v>
+        <v>0.08851176962481448</v>
       </c>
       <c r="X59" s="163" t="n">
-        <v>0.04818497413654178</v>
+        <v>0.04818497413654177</v>
       </c>
       <c r="Y59" s="161" t="n">
-        <v>0.01354935486534161</v>
+        <v>0.0135493548653416</v>
       </c>
       <c r="Z59" s="162" t="n">
-        <v>0.008778002052295262</v>
+        <v>0.00877800205229526</v>
       </c>
       <c r="AA59" s="162" t="n">
-        <v>0.006811992551617332</v>
+        <v>0.00681199255161733</v>
       </c>
       <c r="AB59" s="162" t="n">
-        <v>0.004872887994626439</v>
+        <v>0.004872887994626438</v>
       </c>
       <c r="AC59" s="163" t="n">
         <v>0.00286052127866046</v>
       </c>
       <c r="AD59" s="164" t="n">
-        <v>6027.934700631875</v>
+        <v>6027.934700631873</v>
       </c>
       <c r="AE59" s="165" t="n">
-        <v>4003.004842348078</v>
+        <v>4003.004842348077</v>
       </c>
       <c r="AF59" s="165" t="n">
-        <v>3154.829841117805</v>
+        <v>3154.829841117804</v>
       </c>
       <c r="AG59" s="165" t="n">
-        <v>2270.078206336738</v>
+        <v>2270.078206336737</v>
       </c>
       <c r="AH59" s="166" t="n">
         <v>1344.309809437798</v>
@@ -6742,46 +6742,46 @@
         </is>
       </c>
       <c r="C61" s="161" t="n">
-        <v>0.3072499790918276</v>
+        <v>0.3072499790918274</v>
       </c>
       <c r="D61" s="162" t="n">
         <v>0.182036974231739</v>
       </c>
       <c r="E61" s="162" t="n">
-        <v>0.1301554935482726</v>
+        <v>0.1301554935482725</v>
       </c>
       <c r="F61" s="162" t="n">
-        <v>0.08482475197956925</v>
+        <v>0.08482475197956922</v>
       </c>
       <c r="G61" s="163" t="n">
-        <v>0.04615443294263651</v>
+        <v>0.0461544329426365</v>
       </c>
       <c r="H61" s="161" t="n">
         <v>0.01204700563103024</v>
       </c>
       <c r="I61" s="162" t="n">
-        <v>0.007762590981958274</v>
+        <v>0.007762590981958272</v>
       </c>
       <c r="J61" s="162" t="n">
-        <v>0.006027063251664863</v>
+        <v>0.006027063251664862</v>
       </c>
       <c r="K61" s="162" t="n">
-        <v>0.004313558010967802</v>
+        <v>0.004313558010967801</v>
       </c>
       <c r="L61" s="163" t="n">
-        <v>0.002532748362714865</v>
+        <v>0.002532748362714864</v>
       </c>
       <c r="M61" s="164" t="n">
-        <v>6063.907811009084</v>
+        <v>6063.907811009082</v>
       </c>
       <c r="N61" s="165" t="n">
-        <v>4003.004842348078</v>
+        <v>4003.004842348077</v>
       </c>
       <c r="O61" s="165" t="n">
-        <v>3154.829841117805</v>
+        <v>3154.829841117804</v>
       </c>
       <c r="P61" s="165" t="n">
-        <v>2270.078206336738</v>
+        <v>2270.078206336737</v>
       </c>
       <c r="Q61" s="166" t="n">
         <v>1344.309809437798</v>
@@ -6792,28 +6792,28 @@
         </is>
       </c>
       <c r="T61" s="161" t="n">
-        <v>0.3186375567136396</v>
+        <v>0.3186375567136395</v>
       </c>
       <c r="U61" s="162" t="n">
         <v>0.1888361344771796</v>
       </c>
       <c r="V61" s="162" t="n">
-        <v>0.1350559953421803</v>
+        <v>0.1350559953421802</v>
       </c>
       <c r="W61" s="162" t="n">
-        <v>0.08803767094436789</v>
+        <v>0.08803767094436787</v>
       </c>
       <c r="X61" s="163" t="n">
-        <v>0.04791142512496707</v>
+        <v>0.04791142512496705</v>
       </c>
       <c r="Y61" s="161" t="n">
         <v>0.01351299194529485</v>
       </c>
       <c r="Z61" s="162" t="n">
-        <v>0.008702683193634372</v>
+        <v>0.00870268319363437</v>
       </c>
       <c r="AA61" s="162" t="n">
-        <v>0.006753734217624573</v>
+        <v>0.006753734217624571</v>
       </c>
       <c r="AB61" s="162" t="n">
         <v>0.004831256750411982</v>
@@ -6822,16 +6822,16 @@
         <v>0.002836144278852596</v>
       </c>
       <c r="AD61" s="164" t="n">
-        <v>6063.907811009084</v>
+        <v>6063.907811009082</v>
       </c>
       <c r="AE61" s="165" t="n">
-        <v>4003.004842348078</v>
+        <v>4003.004842348077</v>
       </c>
       <c r="AF61" s="165" t="n">
-        <v>3154.829841117805</v>
+        <v>3154.829841117804</v>
       </c>
       <c r="AG61" s="165" t="n">
-        <v>2270.078206336738</v>
+        <v>2270.078206336737</v>
       </c>
       <c r="AH61" s="166" t="n">
         <v>1344.309809437798</v>
@@ -6844,10 +6844,10 @@
         </is>
       </c>
       <c r="C62" s="155" t="n">
-        <v>0.9687338816240315</v>
+        <v>0.9687338816240311</v>
       </c>
       <c r="D62" s="156" t="n">
-        <v>0.007761950251782546</v>
+        <v>0.007761950251782545</v>
       </c>
       <c r="E62" s="156" t="n">
         <v>0</v>
@@ -6859,10 +6859,10 @@
         <v>0</v>
       </c>
       <c r="H62" s="155" t="n">
-        <v>0.8388632024375809</v>
+        <v>0.8388632024375805</v>
       </c>
       <c r="I62" s="156" t="n">
-        <v>0.00677594847679417</v>
+        <v>0.006775948476794169</v>
       </c>
       <c r="J62" s="156" t="n">
         <v>0</v>
@@ -6874,10 +6874,10 @@
         <v>0</v>
       </c>
       <c r="M62" s="158" t="n">
-        <v>7302.095334324173</v>
+        <v>7302.095334324171</v>
       </c>
       <c r="N62" s="159" t="n">
-        <v>66.70745681680212</v>
+        <v>66.70745681680211</v>
       </c>
       <c r="O62" s="159" t="n">
         <v>0</v>
@@ -6894,10 +6894,10 @@
         </is>
       </c>
       <c r="T62" s="155" t="n">
-        <v>0.6166687724745138</v>
+        <v>0.6166687724745135</v>
       </c>
       <c r="U62" s="156" t="n">
-        <v>0.004941039458381059</v>
+        <v>0.004941039458381058</v>
       </c>
       <c r="V62" s="156" t="n">
         <v>0</v>
@@ -6909,10 +6909,10 @@
         <v>0</v>
       </c>
       <c r="Y62" s="155" t="n">
-        <v>0.5383549422350706</v>
+        <v>0.5383549422350704</v>
       </c>
       <c r="Z62" s="156" t="n">
-        <v>0.004346721070418809</v>
+        <v>0.004346721070418808</v>
       </c>
       <c r="AA62" s="156" t="n">
         <v>0</v>
@@ -6924,10 +6924,10 @@
         <v>0</v>
       </c>
       <c r="AD62" s="158" t="n">
-        <v>7302.095334324173</v>
+        <v>7302.095334324171</v>
       </c>
       <c r="AE62" s="159" t="n">
-        <v>66.70745681680212</v>
+        <v>66.70745681680211</v>
       </c>
       <c r="AF62" s="159" t="n">
         <v>0</v>
@@ -6946,46 +6946,46 @@
         </is>
       </c>
       <c r="C63" s="179" t="n">
-        <v>0.4900667056318948</v>
+        <v>0.4900667056318945</v>
       </c>
       <c r="D63" s="180" t="n">
-        <v>0.1330657255706676</v>
+        <v>0.1330657255706675</v>
       </c>
       <c r="E63" s="180" t="n">
-        <v>0.09278078757621767</v>
+        <v>0.09278078757621762</v>
       </c>
       <c r="F63" s="180" t="n">
         <v>0.05990928242624682</v>
       </c>
       <c r="G63" s="181" t="n">
-        <v>0.03209847261822418</v>
+        <v>0.03209847261822417</v>
       </c>
       <c r="H63" s="179" t="n">
-        <v>0.02610248248120665</v>
+        <v>0.02610248248120663</v>
       </c>
       <c r="I63" s="180" t="n">
-        <v>0.007744108010074377</v>
+        <v>0.007744108010074375</v>
       </c>
       <c r="J63" s="180" t="n">
-        <v>0.005901206540337719</v>
+        <v>0.005901206540337717</v>
       </c>
       <c r="K63" s="180" t="n">
-        <v>0.004212494141847577</v>
+        <v>0.004212494141847576</v>
       </c>
       <c r="L63" s="181" t="n">
-        <v>0.002466183352691457</v>
+        <v>0.002466183352691456</v>
       </c>
       <c r="M63" s="182" t="n">
-        <v>13366.00314533326</v>
+        <v>13366.00314533325</v>
       </c>
       <c r="N63" s="183" t="n">
-        <v>4069.71229916488</v>
+        <v>4069.712299164879</v>
       </c>
       <c r="O63" s="183" t="n">
-        <v>3154.829841117805</v>
+        <v>3154.829841117804</v>
       </c>
       <c r="P63" s="183" t="n">
-        <v>2270.078206336738</v>
+        <v>2270.078206336737</v>
       </c>
       <c r="Q63" s="184" t="n">
         <v>1344.309809437798</v>
@@ -6996,46 +6996,46 @@
         </is>
       </c>
       <c r="T63" s="185" t="n">
-        <v>0.4329499907115915</v>
+        <v>0.4329499907115912</v>
       </c>
       <c r="U63" s="186" t="n">
         <v>0.1172861822149912</v>
       </c>
       <c r="V63" s="186" t="n">
-        <v>0.08152432171014516</v>
+        <v>0.08152432171014515</v>
       </c>
       <c r="W63" s="186" t="n">
-        <v>0.05246369964004858</v>
+        <v>0.05246369964004857</v>
       </c>
       <c r="X63" s="187" t="n">
         <v>0.02795148474709573</v>
       </c>
       <c r="Y63" s="185" t="n">
-        <v>0.02891132977072699</v>
+        <v>0.02891132977072697</v>
       </c>
       <c r="Z63" s="186" t="n">
-        <v>0.00856204269847502</v>
+        <v>0.008562042698475018</v>
       </c>
       <c r="AA63" s="186" t="n">
-        <v>0.006511138532102182</v>
+        <v>0.006511138532102181</v>
       </c>
       <c r="AB63" s="186" t="n">
-        <v>0.004636924322182096</v>
+        <v>0.004636924322182095</v>
       </c>
       <c r="AC63" s="187" t="n">
         <v>0.00270840162347226</v>
       </c>
       <c r="AD63" s="188" t="n">
-        <v>13366.00314533326</v>
+        <v>13366.00314533325</v>
       </c>
       <c r="AE63" s="189" t="n">
-        <v>4069.71229916488</v>
+        <v>4069.712299164879</v>
       </c>
       <c r="AF63" s="189" t="n">
-        <v>3154.829841117805</v>
+        <v>3154.829841117804</v>
       </c>
       <c r="AG63" s="189" t="n">
-        <v>2270.078206336738</v>
+        <v>2270.078206336737</v>
       </c>
       <c r="AH63" s="190" t="n">
         <v>1344.309809437798</v>
@@ -7297,7 +7297,7 @@
         </is>
       </c>
       <c r="C68" s="148" t="n">
-        <v>1.240915775466739</v>
+        <v>1.240915775466738</v>
       </c>
       <c r="D68" s="149" t="n">
         <v>1.435828184104378</v>
@@ -7306,40 +7306,40 @@
         <v>1.558843138619757</v>
       </c>
       <c r="F68" s="149" t="n">
-        <v>1.696084889866562</v>
+        <v>1.696084889866561</v>
       </c>
       <c r="G68" s="150" t="n">
-        <v>1.732744931485474</v>
+        <v>1.732744931485473</v>
       </c>
       <c r="H68" s="148" t="n">
-        <v>0.08062834284557918</v>
+        <v>0.08062834284557914</v>
       </c>
       <c r="I68" s="149" t="n">
         <v>0.1009955524653997</v>
       </c>
       <c r="J68" s="149" t="n">
-        <v>0.1184018057656887</v>
+        <v>0.1184018057656886</v>
       </c>
       <c r="K68" s="149" t="n">
-        <v>0.140684957713206</v>
+        <v>0.1406849577132059</v>
       </c>
       <c r="L68" s="150" t="n">
-        <v>0.1539661671632151</v>
+        <v>0.153966167163215</v>
       </c>
       <c r="M68" s="151" t="n">
-        <v>20128.10303201955</v>
+        <v>20128.10303201954</v>
       </c>
       <c r="N68" s="152" t="n">
         <v>25812.13890823187</v>
       </c>
       <c r="O68" s="152" t="n">
-        <v>30716.76485797621</v>
+        <v>30716.7648579762</v>
       </c>
       <c r="P68" s="152" t="n">
-        <v>36743.42157286885</v>
+        <v>36743.42157286883</v>
       </c>
       <c r="Q68" s="153" t="n">
-        <v>40705.83950187096</v>
+        <v>40705.83950187094</v>
       </c>
       <c r="S68" s="21" t="inlineStr">
         <is>
@@ -7350,46 +7350,46 @@
         <v>1.272474155717303</v>
       </c>
       <c r="U68" s="149" t="n">
-        <v>1.472343484098369</v>
+        <v>1.472343484098368</v>
       </c>
       <c r="V68" s="149" t="n">
         <v>1.598486896473542</v>
       </c>
       <c r="W68" s="149" t="n">
-        <v>1.739218914713263</v>
+        <v>1.739218914713262</v>
       </c>
       <c r="X68" s="150" t="n">
-        <v>1.776811277087769</v>
+        <v>1.776811277087768</v>
       </c>
       <c r="Y68" s="148" t="n">
-        <v>0.09891286787018054</v>
+        <v>0.09891286787018048</v>
       </c>
       <c r="Z68" s="149" t="n">
         <v>0.1237594371337213</v>
       </c>
       <c r="AA68" s="149" t="n">
-        <v>0.1449182773801906</v>
+        <v>0.1449182773801905</v>
       </c>
       <c r="AB68" s="149" t="n">
-        <v>0.1719399395458051</v>
+        <v>0.171939939545805</v>
       </c>
       <c r="AC68" s="150" t="n">
-        <v>0.1879393759480253</v>
+        <v>0.1879393759480252</v>
       </c>
       <c r="AD68" s="151" t="n">
-        <v>20128.10303201955</v>
+        <v>20128.10303201954</v>
       </c>
       <c r="AE68" s="152" t="n">
         <v>25812.13890823187</v>
       </c>
       <c r="AF68" s="152" t="n">
-        <v>30716.76485797621</v>
+        <v>30716.7648579762</v>
       </c>
       <c r="AG68" s="152" t="n">
-        <v>36743.42157286885</v>
+        <v>36743.42157286883</v>
       </c>
       <c r="AH68" s="153" t="n">
-        <v>40705.83950187096</v>
+        <v>40705.83950187094</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -7399,40 +7399,40 @@
         </is>
       </c>
       <c r="C69" s="155" t="n">
-        <v>2.258930224508234</v>
+        <v>2.258930224508235</v>
       </c>
       <c r="D69" s="156" t="n">
-        <v>2.728325982645054</v>
+        <v>2.728325982645053</v>
       </c>
       <c r="E69" s="156" t="n">
-        <v>3.094889169146736</v>
+        <v>3.094889169146735</v>
       </c>
       <c r="F69" s="156" t="n">
-        <v>3.460659809672958</v>
+        <v>3.460659809672957</v>
       </c>
       <c r="G69" s="157" t="n">
-        <v>3.825158607543029</v>
+        <v>3.825158607543028</v>
       </c>
       <c r="H69" s="155" t="n">
-        <v>0.0309014938455898</v>
+        <v>0.03090149384558982</v>
       </c>
       <c r="I69" s="156" t="n">
         <v>0.041555901251062</v>
       </c>
       <c r="J69" s="156" t="n">
-        <v>0.05244120731052446</v>
+        <v>0.05244120731052444</v>
       </c>
       <c r="K69" s="156" t="n">
-        <v>0.06562204799571857</v>
+        <v>0.06562204799571855</v>
       </c>
       <c r="L69" s="157" t="n">
-        <v>0.07966481862190693</v>
+        <v>0.07966481862190691</v>
       </c>
       <c r="M69" s="158" t="n">
-        <v>7718.910238380733</v>
+        <v>7718.910238380738</v>
       </c>
       <c r="N69" s="159" t="n">
-        <v>10642.04347605476</v>
+        <v>10642.04347605475</v>
       </c>
       <c r="O69" s="159" t="n">
         <v>13632.28457542605</v>
@@ -7449,40 +7449,40 @@
         </is>
       </c>
       <c r="T69" s="155" t="n">
-        <v>2.473044786201486</v>
+        <v>2.473044786201488</v>
       </c>
       <c r="U69" s="156" t="n">
-        <v>2.986932607848597</v>
+        <v>2.986932607848596</v>
       </c>
       <c r="V69" s="156" t="n">
-        <v>3.388240787869403</v>
+        <v>3.388240787869401</v>
       </c>
       <c r="W69" s="156" t="n">
-        <v>3.788681299791755</v>
+        <v>3.788681299791754</v>
       </c>
       <c r="X69" s="157" t="n">
-        <v>4.187729416404355</v>
+        <v>4.187729416404354</v>
       </c>
       <c r="Y69" s="155" t="n">
-        <v>0.03197640434225306</v>
+        <v>0.03197640434225308</v>
       </c>
       <c r="Z69" s="156" t="n">
-        <v>0.04300513370332971</v>
+        <v>0.0430051337033297</v>
       </c>
       <c r="AA69" s="156" t="n">
-        <v>0.0542752241914889</v>
+        <v>0.05427522419148888</v>
       </c>
       <c r="AB69" s="156" t="n">
-        <v>0.06792465336478562</v>
+        <v>0.06792465336478561</v>
       </c>
       <c r="AC69" s="157" t="n">
-        <v>0.0824687146861951</v>
+        <v>0.08246871468619509</v>
       </c>
       <c r="AD69" s="158" t="n">
-        <v>7718.910238380733</v>
+        <v>7718.910238380738</v>
       </c>
       <c r="AE69" s="159" t="n">
-        <v>10642.04347605476</v>
+        <v>10642.04347605475</v>
       </c>
       <c r="AF69" s="159" t="n">
         <v>13632.28457542605</v>
@@ -7504,25 +7504,25 @@
         <v>1.418058184005969</v>
       </c>
       <c r="D70" s="162" t="n">
-        <v>1.666267109737836</v>
+        <v>1.666267109737835</v>
       </c>
       <c r="E70" s="162" t="n">
-        <v>1.839475282027226</v>
+        <v>1.839475282027225</v>
       </c>
       <c r="F70" s="162" t="n">
-        <v>2.024248889142525</v>
+        <v>2.024248889142524</v>
       </c>
       <c r="G70" s="163" t="n">
-        <v>2.127487192433817</v>
+        <v>2.127487192433816</v>
       </c>
       <c r="H70" s="161" t="n">
-        <v>0.05575743566650466</v>
+        <v>0.05575743566650465</v>
       </c>
       <c r="I70" s="162" t="n">
-        <v>0.07124593895665754</v>
+        <v>0.07124593895665753</v>
       </c>
       <c r="J70" s="162" t="n">
-        <v>0.08538813797827198</v>
+        <v>0.08538813797827194</v>
       </c>
       <c r="K70" s="162" t="n">
         <v>0.1031655390887182</v>
@@ -7531,19 +7531,19 @@
         <v>0.1169637577110555</v>
       </c>
       <c r="M70" s="164" t="n">
-        <v>27847.01327040028</v>
+        <v>27847.01327040027</v>
       </c>
       <c r="N70" s="165" t="n">
-        <v>36454.18238428663</v>
+        <v>36454.18238428662</v>
       </c>
       <c r="O70" s="165" t="n">
-        <v>44349.04943340226</v>
+        <v>44349.04943340224</v>
       </c>
       <c r="P70" s="165" t="n">
-        <v>53871.28365771406</v>
+        <v>53871.28365771403</v>
       </c>
       <c r="Q70" s="166" t="n">
-        <v>61600.31695509894</v>
+        <v>61600.31695509891</v>
       </c>
       <c r="S70" s="42" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="T70" s="161" t="n">
-        <v>1.470329493561123</v>
+        <v>1.470329493561122</v>
       </c>
       <c r="U70" s="162" t="n">
         <v>1.728161690813588</v>
@@ -7560,40 +7560,40 @@
         <v>1.90834279372576</v>
       </c>
       <c r="W70" s="162" t="n">
-        <v>2.100475056407511</v>
+        <v>2.10047505640751</v>
       </c>
       <c r="X70" s="163" t="n">
-        <v>2.207980376581161</v>
+        <v>2.20798037658116</v>
       </c>
       <c r="Y70" s="161" t="n">
-        <v>0.06259342270263463</v>
+        <v>0.06259342270263461</v>
       </c>
       <c r="Z70" s="162" t="n">
-        <v>0.07993867116990835</v>
+        <v>0.07993867116990834</v>
       </c>
       <c r="AA70" s="162" t="n">
-        <v>0.09575964778645697</v>
+        <v>0.09575964778645693</v>
       </c>
       <c r="AB70" s="162" t="n">
-        <v>0.1156386289503237</v>
+        <v>0.1156386289503236</v>
       </c>
       <c r="AC70" s="163" t="n">
         <v>0.1310776847607631</v>
       </c>
       <c r="AD70" s="164" t="n">
-        <v>27847.01327040028</v>
+        <v>27847.01327040027</v>
       </c>
       <c r="AE70" s="165" t="n">
-        <v>36454.18238428663</v>
+        <v>36454.18238428662</v>
       </c>
       <c r="AF70" s="165" t="n">
-        <v>44349.04943340226</v>
+        <v>44349.04943340224</v>
       </c>
       <c r="AG70" s="165" t="n">
-        <v>53871.28365771406</v>
+        <v>53871.28365771403</v>
       </c>
       <c r="AH70" s="166" t="n">
-        <v>61600.31695509894</v>
+        <v>61600.31695509891</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" thickBot="1">
@@ -7609,7 +7609,7 @@
         <v>6.89716472165587</v>
       </c>
       <c r="E71" s="156" t="n">
-        <v>7.797752674231765</v>
+        <v>7.797752674231762</v>
       </c>
       <c r="F71" s="156" t="n">
         <v>8.438751779830351</v>
@@ -7624,7 +7624,7 @@
         <v>0.1930694997361621</v>
       </c>
       <c r="J71" s="156" t="n">
-        <v>0.2482277182544588</v>
+        <v>0.2482277182544587</v>
       </c>
       <c r="K71" s="156" t="n">
         <v>0.3079699198303258</v>
@@ -7659,7 +7659,7 @@
         <v>7.440972914296981</v>
       </c>
       <c r="V71" s="156" t="n">
-        <v>8.412567885926215</v>
+        <v>8.412567885926213</v>
       </c>
       <c r="W71" s="156" t="n">
         <v>9.10410668126219</v>
@@ -7674,7 +7674,7 @@
         <v>0.1962680910673681</v>
       </c>
       <c r="AA71" s="156" t="n">
-        <v>0.2523976884265097</v>
+        <v>0.2523976884265096</v>
       </c>
       <c r="AB71" s="156" t="n">
         <v>0.3132302324265582</v>
@@ -7714,19 +7714,19 @@
         <v>1.871261515524443</v>
       </c>
       <c r="F72" s="162" t="n">
-        <v>2.059963334284018</v>
+        <v>2.059963334284017</v>
       </c>
       <c r="G72" s="163" t="n">
-        <v>2.16792246212049</v>
+        <v>2.167922462120489</v>
       </c>
       <c r="H72" s="161" t="n">
-        <v>0.05646612807599403</v>
+        <v>0.05646612807599401</v>
       </c>
       <c r="I72" s="162" t="n">
-        <v>0.07219376556867026</v>
+        <v>0.07219376556867024</v>
       </c>
       <c r="J72" s="162" t="n">
-        <v>0.08665182857064088</v>
+        <v>0.08665182857064084</v>
       </c>
       <c r="K72" s="162" t="n">
         <v>0.1047544630020372</v>
@@ -7738,16 +7738,16 @@
         <v>28422.44833151767</v>
       </c>
       <c r="N72" s="165" t="n">
-        <v>37228.80592709327</v>
+        <v>37228.80592709326</v>
       </c>
       <c r="O72" s="165" t="n">
-        <v>45357.37607972978</v>
+        <v>45357.37607972976</v>
       </c>
       <c r="P72" s="165" t="n">
-        <v>55128.69489010979</v>
+        <v>55128.69489010976</v>
       </c>
       <c r="Q72" s="166" t="n">
-        <v>63143.65156541426</v>
+        <v>63143.65156541423</v>
       </c>
       <c r="S72" s="42" t="inlineStr">
         <is>
@@ -7758,46 +7758,46 @@
         <v>1.493502172927557</v>
       </c>
       <c r="U72" s="162" t="n">
-        <v>1.756216662068706</v>
+        <v>1.756216662068705</v>
       </c>
       <c r="V72" s="162" t="n">
-        <v>1.941716631660567</v>
+        <v>1.941716631660566</v>
       </c>
       <c r="W72" s="162" t="n">
-        <v>2.137988852886243</v>
+        <v>2.137988852886242</v>
       </c>
       <c r="X72" s="163" t="n">
-        <v>2.250450240602322</v>
+        <v>2.250450240602321</v>
       </c>
       <c r="Y72" s="161" t="n">
-        <v>0.06333742651431316</v>
+        <v>0.06333742651431315</v>
       </c>
       <c r="Z72" s="162" t="n">
-        <v>0.08093682531514111</v>
+        <v>0.0809368253151411</v>
       </c>
       <c r="AA72" s="162" t="n">
-        <v>0.09709926629285315</v>
+        <v>0.09709926629285309</v>
       </c>
       <c r="AB72" s="162" t="n">
-        <v>0.1173267416892408</v>
+        <v>0.1173267416892407</v>
       </c>
       <c r="AC72" s="163" t="n">
-        <v>0.1332166922206765</v>
+        <v>0.1332166922206764</v>
       </c>
       <c r="AD72" s="164" t="n">
         <v>28422.44833151767</v>
       </c>
       <c r="AE72" s="165" t="n">
-        <v>37228.80592709327</v>
+        <v>37228.80592709326</v>
       </c>
       <c r="AF72" s="165" t="n">
-        <v>45357.37607972978</v>
+        <v>45357.37607972976</v>
       </c>
       <c r="AG72" s="165" t="n">
-        <v>55128.69489010979</v>
+        <v>55128.69489010976</v>
       </c>
       <c r="AH72" s="166" t="n">
-        <v>63143.65156541426</v>
+        <v>63143.65156541423</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" thickBot="1">
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="C73" s="155" t="n">
-        <v>56.76488184947281</v>
+        <v>56.76488184947279</v>
       </c>
       <c r="D73" s="156" t="n">
-        <v>75.4083384046809</v>
+        <v>75.40833840468089</v>
       </c>
       <c r="E73" s="156" t="n">
-        <v>20.13026823107952</v>
+        <v>20.13026823107951</v>
       </c>
       <c r="F73" s="156" t="n">
         <v>21.77160733293182</v>
@@ -7822,13 +7822,13 @@
         <v>23.46399005135553</v>
       </c>
       <c r="H73" s="155" t="n">
-        <v>49.15485199548367</v>
+        <v>49.15485199548366</v>
       </c>
       <c r="I73" s="156" t="n">
-        <v>65.82920518376594</v>
+        <v>65.82920518376591</v>
       </c>
       <c r="J73" s="156" t="n">
-        <v>17.60665982721789</v>
+        <v>17.60665982721788</v>
       </c>
       <c r="K73" s="156" t="n">
         <v>19.19207292214616</v>
@@ -7840,16 +7840,16 @@
         <v>427880.7490573226</v>
       </c>
       <c r="N73" s="159" t="n">
-        <v>648071.4658795752</v>
+        <v>648071.465879575</v>
       </c>
       <c r="O73" s="159" t="n">
-        <v>196554.3811374283</v>
+        <v>196554.3811374282</v>
       </c>
       <c r="P73" s="159" t="n">
         <v>242316.8820399614</v>
       </c>
       <c r="Q73" s="160" t="n">
-        <v>299270.5413708418</v>
+        <v>299270.5413708417</v>
       </c>
       <c r="S73" s="32" t="inlineStr">
         <is>
@@ -7857,10 +7857,10 @@
         </is>
       </c>
       <c r="T73" s="155" t="n">
-        <v>36.13492897666688</v>
+        <v>36.13492897666687</v>
       </c>
       <c r="U73" s="156" t="n">
-        <v>48.00282963201328</v>
+        <v>48.00282963201327</v>
       </c>
       <c r="V73" s="156" t="n">
         <v>12.81436319624908</v>
@@ -7872,10 +7872,10 @@
         <v>14.93651684616031</v>
       </c>
       <c r="Y73" s="155" t="n">
-        <v>31.54597487374127</v>
+        <v>31.54597487374126</v>
       </c>
       <c r="Z73" s="156" t="n">
-        <v>42.22895055963846</v>
+        <v>42.22895055963844</v>
       </c>
       <c r="AA73" s="156" t="n">
         <v>11.29339756109872</v>
@@ -7890,16 +7890,16 @@
         <v>427880.7490573226</v>
       </c>
       <c r="AE73" s="159" t="n">
-        <v>648071.4658795752</v>
+        <v>648071.465879575</v>
       </c>
       <c r="AF73" s="159" t="n">
-        <v>196554.3811374283</v>
+        <v>196554.3811374282</v>
       </c>
       <c r="AG73" s="159" t="n">
         <v>242316.8820399614</v>
       </c>
       <c r="AH73" s="160" t="n">
-        <v>299270.5413708418</v>
+        <v>299270.5413708417</v>
       </c>
     </row>
     <row r="74" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -7909,49 +7909,49 @@
         </is>
       </c>
       <c r="C74" s="179" t="n">
-        <v>16.73043184878539</v>
+        <v>16.73043184878538</v>
       </c>
       <c r="D74" s="180" t="n">
-        <v>22.40698388444868</v>
+        <v>22.40698388444867</v>
       </c>
       <c r="E74" s="180" t="n">
-        <v>7.114413292921737</v>
+        <v>7.114413292921733</v>
       </c>
       <c r="F74" s="180" t="n">
         <v>7.849840161893622</v>
       </c>
       <c r="G74" s="181" t="n">
-        <v>8.653468096974779</v>
+        <v>8.653468096974775</v>
       </c>
       <c r="H74" s="179" t="n">
-        <v>0.8911150241738037</v>
+        <v>0.8911150241738036</v>
       </c>
       <c r="I74" s="180" t="n">
         <v>1.304033045602067</v>
       </c>
       <c r="J74" s="180" t="n">
-        <v>0.4525034045476991</v>
+        <v>0.4525034045476989</v>
       </c>
       <c r="K74" s="180" t="n">
         <v>0.5519579663990363</v>
       </c>
       <c r="L74" s="181" t="n">
-        <v>0.6648615096934321</v>
+        <v>0.6648615096934318</v>
       </c>
       <c r="M74" s="182" t="n">
         <v>456303.1973888403</v>
       </c>
       <c r="N74" s="183" t="n">
-        <v>685300.2718066685</v>
+        <v>685300.2718066683</v>
       </c>
       <c r="O74" s="183" t="n">
-        <v>241911.7572171581</v>
+        <v>241911.757217158</v>
       </c>
       <c r="P74" s="183" t="n">
         <v>297445.5769300712</v>
       </c>
       <c r="Q74" s="184" t="n">
-        <v>362414.1929362561</v>
+        <v>362414.1929362559</v>
       </c>
       <c r="S74" s="51" t="inlineStr">
         <is>
@@ -7962,46 +7962,46 @@
         <v>14.78051912176489</v>
       </c>
       <c r="U74" s="186" t="n">
-        <v>19.74986108172646</v>
+        <v>19.74986108172645</v>
       </c>
       <c r="V74" s="186" t="n">
-        <v>6.251269613276646</v>
+        <v>6.251269613276644</v>
       </c>
       <c r="W74" s="186" t="n">
         <v>6.87425453614764</v>
       </c>
       <c r="X74" s="187" t="n">
-        <v>7.535476357362319</v>
+        <v>7.535476357362317</v>
       </c>
       <c r="Y74" s="185" t="n">
-        <v>0.9870065173336426</v>
+        <v>0.9870065173336425</v>
       </c>
       <c r="Z74" s="186" t="n">
-        <v>1.441765352722668</v>
+        <v>1.441765352722667</v>
       </c>
       <c r="AA74" s="186" t="n">
-        <v>0.4992728746432474</v>
+        <v>0.4992728746432472</v>
       </c>
       <c r="AB74" s="186" t="n">
         <v>0.607570534945676</v>
       </c>
       <c r="AC74" s="187" t="n">
-        <v>0.7301614416757422</v>
+        <v>0.7301614416757419</v>
       </c>
       <c r="AD74" s="188" t="n">
         <v>456303.1973888403</v>
       </c>
       <c r="AE74" s="189" t="n">
-        <v>685300.2718066685</v>
+        <v>685300.2718066683</v>
       </c>
       <c r="AF74" s="189" t="n">
-        <v>241911.7572171581</v>
+        <v>241911.757217158</v>
       </c>
       <c r="AG74" s="189" t="n">
         <v>297445.5769300712</v>
       </c>
       <c r="AH74" s="190" t="n">
-        <v>362414.1929362561</v>
+        <v>362414.1929362559</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" thickBot="1"/>
@@ -8260,46 +8260,46 @@
         </is>
       </c>
       <c r="C79" s="148" t="n">
-        <v>441.603906823645</v>
+        <v>441.6039068236449</v>
       </c>
       <c r="D79" s="149" t="n">
-        <v>487.9426072806427</v>
+        <v>487.9426072806424</v>
       </c>
       <c r="E79" s="149" t="n">
-        <v>526.9971134959333</v>
+        <v>526.9971134959329</v>
       </c>
       <c r="F79" s="149" t="n">
-        <v>566.6008940872617</v>
+        <v>566.6008940872615</v>
       </c>
       <c r="G79" s="150" t="n">
-        <v>614.1759533263676</v>
+        <v>614.1759533263674</v>
       </c>
       <c r="H79" s="148" t="n">
         <v>28.69315702585201</v>
       </c>
       <c r="I79" s="149" t="n">
-        <v>34.32167841478561</v>
+        <v>34.32167841478559</v>
       </c>
       <c r="J79" s="149" t="n">
-        <v>40.02802355500148</v>
+        <v>40.02802355500145</v>
       </c>
       <c r="K79" s="149" t="n">
-        <v>46.99777900338609</v>
+        <v>46.99777900338607</v>
       </c>
       <c r="L79" s="150" t="n">
         <v>54.57370890498387</v>
       </c>
       <c r="M79" s="151" t="n">
-        <v>7162975.208809355</v>
+        <v>7162975.208809353</v>
       </c>
       <c r="N79" s="152" t="n">
-        <v>8771831.127015397</v>
+        <v>8771831.127015393</v>
       </c>
       <c r="O79" s="152" t="n">
         <v>10384397.25912369</v>
       </c>
       <c r="P79" s="152" t="n">
-        <v>12274654.19885356</v>
+        <v>12274654.19885355</v>
       </c>
       <c r="Q79" s="153" t="n">
         <v>14428290.81634009</v>
@@ -8310,46 +8310,46 @@
         </is>
       </c>
       <c r="T79" s="148" t="n">
-        <v>452.8345675076336</v>
+        <v>452.8345675076335</v>
       </c>
       <c r="U79" s="149" t="n">
-        <v>500.3517317719663</v>
+        <v>500.3517317719661</v>
       </c>
       <c r="V79" s="149" t="n">
-        <v>540.3994536284849</v>
+        <v>540.3994536284847</v>
       </c>
       <c r="W79" s="149" t="n">
-        <v>581.0104187459277</v>
+        <v>581.0104187459275</v>
       </c>
       <c r="X79" s="150" t="n">
-        <v>629.7953842813299</v>
+        <v>629.7953842813298</v>
       </c>
       <c r="Y79" s="148" t="n">
         <v>35.20005930311707</v>
       </c>
       <c r="Z79" s="149" t="n">
-        <v>42.05761044332785</v>
+        <v>42.05761044332782</v>
       </c>
       <c r="AA79" s="149" t="n">
-        <v>48.99243033509123</v>
+        <v>48.9924303350912</v>
       </c>
       <c r="AB79" s="149" t="n">
-        <v>57.43894309654952</v>
+        <v>57.43894309654949</v>
       </c>
       <c r="AC79" s="150" t="n">
         <v>66.61560123075081</v>
       </c>
       <c r="AD79" s="151" t="n">
-        <v>7162975.208809355</v>
+        <v>7162975.208809353</v>
       </c>
       <c r="AE79" s="152" t="n">
-        <v>8771831.127015397</v>
+        <v>8771831.127015393</v>
       </c>
       <c r="AF79" s="152" t="n">
         <v>10384397.25912369</v>
       </c>
       <c r="AG79" s="152" t="n">
-        <v>12274654.19885356</v>
+        <v>12274654.19885355</v>
       </c>
       <c r="AH79" s="153" t="n">
         <v>14428290.81634009</v>
@@ -8362,10 +8362,10 @@
         </is>
       </c>
       <c r="C80" s="155" t="n">
-        <v>935.936326290573</v>
+        <v>935.9363262905729</v>
       </c>
       <c r="D80" s="156" t="n">
-        <v>1047.38053267149</v>
+        <v>1047.380532671491</v>
       </c>
       <c r="E80" s="156" t="n">
         <v>1135.89205270745</v>
@@ -8383,7 +8383,7 @@
         <v>15.95294780200157</v>
       </c>
       <c r="J80" s="156" t="n">
-        <v>19.24707069068693</v>
+        <v>19.24707069068692</v>
       </c>
       <c r="K80" s="156" t="n">
         <v>23.24222907536832</v>
@@ -8392,19 +8392,19 @@
         <v>27.93957296870531</v>
       </c>
       <c r="M80" s="158" t="n">
-        <v>3198154.77835288</v>
+        <v>3198154.778352879</v>
       </c>
       <c r="N80" s="159" t="n">
-        <v>4085387.609679002</v>
+        <v>4085387.609679003</v>
       </c>
       <c r="O80" s="159" t="n">
-        <v>5003346.764027088</v>
+        <v>5003346.764027087</v>
       </c>
       <c r="P80" s="159" t="n">
         <v>6066401.557190973</v>
       </c>
       <c r="Q80" s="160" t="n">
-        <v>7327987.279028301</v>
+        <v>7327987.2790283</v>
       </c>
       <c r="S80" s="32" t="inlineStr">
         <is>
@@ -8415,10 +8415,10 @@
         <v>1024.649821777192</v>
       </c>
       <c r="U80" s="156" t="n">
-        <v>1146.657359040849</v>
+        <v>1146.65735904085</v>
       </c>
       <c r="V80" s="156" t="n">
-        <v>1243.558516397913</v>
+        <v>1243.558516397912</v>
       </c>
       <c r="W80" s="156" t="n">
         <v>1341.887389266933</v>
@@ -8439,22 +8439,22 @@
         <v>24.05777328790984</v>
       </c>
       <c r="AC80" s="157" t="n">
-        <v>28.92293877609702</v>
+        <v>28.92293877609701</v>
       </c>
       <c r="AD80" s="158" t="n">
-        <v>3198154.77835288</v>
+        <v>3198154.778352879</v>
       </c>
       <c r="AE80" s="159" t="n">
-        <v>4085387.609679002</v>
+        <v>4085387.609679003</v>
       </c>
       <c r="AF80" s="159" t="n">
-        <v>5003346.764027088</v>
+        <v>5003346.764027087</v>
       </c>
       <c r="AG80" s="159" t="n">
         <v>6066401.557190973</v>
       </c>
       <c r="AH80" s="160" t="n">
-        <v>7327987.279028301</v>
+        <v>7327987.2790283</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" thickTop="1">
@@ -8464,43 +8464,43 @@
         </is>
       </c>
       <c r="C81" s="161" t="n">
-        <v>527.6215812150497</v>
+        <v>527.6215812150496</v>
       </c>
       <c r="D81" s="162" t="n">
-        <v>587.6845756083513</v>
+        <v>587.6845756083511</v>
       </c>
       <c r="E81" s="162" t="n">
-        <v>638.2408448066839</v>
+        <v>638.2408448066836</v>
       </c>
       <c r="F81" s="162" t="n">
-        <v>689.1772242846473</v>
+        <v>689.1772242846472</v>
       </c>
       <c r="G81" s="163" t="n">
-        <v>751.3955331863489</v>
+        <v>751.3955331863488</v>
       </c>
       <c r="H81" s="161" t="n">
-        <v>20.74585281666678</v>
+        <v>20.74585281666677</v>
       </c>
       <c r="I81" s="162" t="n">
-        <v>25.12810770546235</v>
+        <v>25.12810770546234</v>
       </c>
       <c r="J81" s="162" t="n">
-        <v>29.62703432451742</v>
+        <v>29.62703432451741</v>
       </c>
       <c r="K81" s="162" t="n">
         <v>35.12381320911081</v>
       </c>
       <c r="L81" s="163" t="n">
-        <v>41.3097880924195</v>
+        <v>41.30978809241949</v>
       </c>
       <c r="M81" s="164" t="n">
-        <v>10361129.98716224</v>
+        <v>10361129.98716223</v>
       </c>
       <c r="N81" s="165" t="n">
         <v>12857218.7366944</v>
       </c>
       <c r="O81" s="165" t="n">
-        <v>15387744.02315078</v>
+        <v>15387744.02315077</v>
       </c>
       <c r="P81" s="165" t="n">
         <v>18341055.75604453</v>
@@ -8514,43 +8514,43 @@
         </is>
       </c>
       <c r="T81" s="161" t="n">
-        <v>547.070339602213</v>
+        <v>547.0703396022128</v>
       </c>
       <c r="U81" s="162" t="n">
-        <v>609.5145033548597</v>
+        <v>609.5145033548596</v>
       </c>
       <c r="V81" s="162" t="n">
-        <v>662.135734439431</v>
+        <v>662.1357344394306</v>
       </c>
       <c r="W81" s="162" t="n">
-        <v>715.1292396990133</v>
+        <v>715.1292396990132</v>
       </c>
       <c r="X81" s="163" t="n">
-        <v>779.8244794264762</v>
+        <v>779.824479426476</v>
       </c>
       <c r="Y81" s="161" t="n">
         <v>23.28934103869398</v>
       </c>
       <c r="Z81" s="162" t="n">
-        <v>28.19399348797961</v>
+        <v>28.1939934879796</v>
       </c>
       <c r="AA81" s="162" t="n">
-        <v>33.22562640486419</v>
+        <v>33.22562640486417</v>
       </c>
       <c r="AB81" s="162" t="n">
         <v>39.37041030257176</v>
       </c>
       <c r="AC81" s="163" t="n">
-        <v>46.29460857857065</v>
+        <v>46.29460857857064</v>
       </c>
       <c r="AD81" s="164" t="n">
-        <v>10361129.98716224</v>
+        <v>10361129.98716223</v>
       </c>
       <c r="AE81" s="165" t="n">
         <v>12857218.7366944</v>
       </c>
       <c r="AF81" s="165" t="n">
-        <v>15387744.02315078</v>
+        <v>15387744.02315077</v>
       </c>
       <c r="AG81" s="165" t="n">
         <v>18341055.75604453</v>
@@ -8566,7 +8566,7 @@
         </is>
       </c>
       <c r="C82" s="155" t="n">
-        <v>1189.636597559711</v>
+        <v>1189.636597559712</v>
       </c>
       <c r="D82" s="156" t="n">
         <v>1325.569639666503</v>
@@ -8575,22 +8575,22 @@
         <v>1423.025396638752</v>
       </c>
       <c r="F82" s="156" t="n">
-        <v>1513.542696414575</v>
+        <v>1513.542696414576</v>
       </c>
       <c r="G82" s="157" t="n">
         <v>1605.136437149781</v>
       </c>
       <c r="H82" s="155" t="n">
-        <v>29.91738499317221</v>
+        <v>29.91738499317222</v>
       </c>
       <c r="I82" s="156" t="n">
         <v>37.10612657869268</v>
       </c>
       <c r="J82" s="156" t="n">
-        <v>45.2995064069</v>
+        <v>45.29950640690001</v>
       </c>
       <c r="K82" s="156" t="n">
-        <v>55.23632345587758</v>
+        <v>55.23632345587759</v>
       </c>
       <c r="L82" s="157" t="n">
         <v>67.12063283633506</v>
@@ -8622,10 +8622,10 @@
         <v>1430.084416253412</v>
       </c>
       <c r="V82" s="156" t="n">
-        <v>1535.224089907415</v>
+        <v>1535.224089907416</v>
       </c>
       <c r="W82" s="156" t="n">
-        <v>1632.878242459756</v>
+        <v>1632.878242459757</v>
       </c>
       <c r="X82" s="157" t="n">
         <v>1731.693708152474</v>
@@ -8637,7 +8637,7 @@
         <v>37.72086549380579</v>
       </c>
       <c r="AA82" s="156" t="n">
-        <v>46.06049148887929</v>
+        <v>46.0604914888793</v>
       </c>
       <c r="AB82" s="156" t="n">
         <v>56.17979328632273</v>
@@ -8668,49 +8668,49 @@
         </is>
       </c>
       <c r="C83" s="161" t="n">
-        <v>530.9305001625936</v>
+        <v>530.9305001625935</v>
       </c>
       <c r="D83" s="162" t="n">
-        <v>591.4531952419994</v>
+        <v>591.4531952419992</v>
       </c>
       <c r="E83" s="162" t="n">
-        <v>642.427515444439</v>
+        <v>642.4275154444388</v>
       </c>
       <c r="F83" s="162" t="n">
-        <v>693.7670975659685</v>
+        <v>693.7670975659684</v>
       </c>
       <c r="G83" s="163" t="n">
-        <v>756.4326620933437</v>
+        <v>756.4326620933435</v>
       </c>
       <c r="H83" s="161" t="n">
-        <v>20.81732517623009</v>
+        <v>20.81732517623007</v>
       </c>
       <c r="I83" s="162" t="n">
-        <v>25.22130055727685</v>
+        <v>25.22130055727684</v>
       </c>
       <c r="J83" s="162" t="n">
-        <v>29.74865804459874</v>
+        <v>29.74865804459873</v>
       </c>
       <c r="K83" s="162" t="n">
-        <v>35.27985112378941</v>
+        <v>35.2798511237894</v>
       </c>
       <c r="L83" s="163" t="n">
-        <v>41.50963329572481</v>
+        <v>41.5096332957248</v>
       </c>
       <c r="M83" s="164" t="n">
-        <v>10478482.7538644</v>
+        <v>10478482.75386439</v>
       </c>
       <c r="N83" s="165" t="n">
         <v>13006094.03429188</v>
       </c>
       <c r="O83" s="165" t="n">
-        <v>15571755.29996048</v>
+        <v>15571755.29996047</v>
       </c>
       <c r="P83" s="165" t="n">
-        <v>18566580.29294713</v>
+        <v>18566580.29294712</v>
       </c>
       <c r="Q83" s="166" t="n">
-        <v>22032116.59203068</v>
+        <v>22032116.59203067</v>
       </c>
       <c r="S83" s="42" t="inlineStr">
         <is>
@@ -8718,49 +8718,49 @@
         </is>
       </c>
       <c r="T83" s="161" t="n">
-        <v>550.6083282954381</v>
+        <v>550.6083282954379</v>
       </c>
       <c r="U83" s="162" t="n">
-        <v>613.5442295997165</v>
+        <v>613.5442295997162</v>
       </c>
       <c r="V83" s="162" t="n">
-        <v>666.6156392497819</v>
+        <v>666.6156392497817</v>
       </c>
       <c r="W83" s="162" t="n">
-        <v>720.0450107092912</v>
+        <v>720.045010709291</v>
       </c>
       <c r="X83" s="163" t="n">
-        <v>785.2282985906941</v>
+        <v>785.2282985906938</v>
       </c>
       <c r="Y83" s="161" t="n">
-        <v>23.35056162872601</v>
+        <v>23.35056162872599</v>
       </c>
       <c r="Z83" s="162" t="n">
         <v>28.27573795805518</v>
       </c>
       <c r="AA83" s="162" t="n">
-        <v>33.33539426663893</v>
+        <v>33.33539426663891</v>
       </c>
       <c r="AB83" s="162" t="n">
-        <v>39.51402031964225</v>
+        <v>39.51402031964224</v>
       </c>
       <c r="AC83" s="163" t="n">
-        <v>46.48203932219572</v>
+        <v>46.48203932219571</v>
       </c>
       <c r="AD83" s="164" t="n">
-        <v>10478482.7538644</v>
+        <v>10478482.75386439</v>
       </c>
       <c r="AE83" s="165" t="n">
         <v>13006094.03429188</v>
       </c>
       <c r="AF83" s="165" t="n">
-        <v>15571755.29996048</v>
+        <v>15571755.29996047</v>
       </c>
       <c r="AG83" s="165" t="n">
-        <v>18566580.29294713</v>
+        <v>18566580.29294712</v>
       </c>
       <c r="AH83" s="166" t="n">
-        <v>22032116.59203068</v>
+        <v>22032116.59203067</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" thickBot="1">
@@ -8770,49 +8770,49 @@
         </is>
       </c>
       <c r="C84" s="155" t="n">
-        <v>970.5424216220611</v>
+        <v>970.5424216220608</v>
       </c>
       <c r="D84" s="156" t="n">
         <v>1025.421756854298</v>
       </c>
       <c r="E84" s="156" t="n">
-        <v>903.2749794753763</v>
+        <v>903.2749794753761</v>
       </c>
       <c r="F84" s="156" t="n">
-        <v>944.9704026104797</v>
+        <v>944.9704026104795</v>
       </c>
       <c r="G84" s="157" t="n">
-        <v>988.5509880948354</v>
+        <v>988.5509880948351</v>
       </c>
       <c r="H84" s="155" t="n">
-        <v>840.4292854282369</v>
+        <v>840.4292854282367</v>
       </c>
       <c r="I84" s="156" t="n">
-        <v>895.1622679922249</v>
+        <v>895.1622679922247</v>
       </c>
       <c r="J84" s="156" t="n">
-        <v>790.0369290413231</v>
+        <v>790.0369290413229</v>
       </c>
       <c r="K84" s="156" t="n">
-        <v>833.00881734798</v>
+        <v>833.0088173479797</v>
       </c>
       <c r="L84" s="157" t="n">
-        <v>880.1024169357395</v>
+        <v>880.1024169357394</v>
       </c>
       <c r="M84" s="158" t="n">
-        <v>7315727.696866723</v>
+        <v>7315727.696866722</v>
       </c>
       <c r="N84" s="159" t="n">
-        <v>8812640.553662211</v>
+        <v>8812640.553662209</v>
       </c>
       <c r="O84" s="159" t="n">
-        <v>8819686.481553895</v>
+        <v>8819686.481553894</v>
       </c>
       <c r="P84" s="159" t="n">
-        <v>10517472.50807059</v>
+        <v>10517472.50807058</v>
       </c>
       <c r="Q84" s="160" t="n">
-        <v>12608434.82853126</v>
+        <v>12608434.82853125</v>
       </c>
       <c r="S84" s="32" t="inlineStr">
         <is>
@@ -8820,49 +8820,49 @@
         </is>
       </c>
       <c r="T84" s="155" t="n">
-        <v>617.8200382263489</v>
+        <v>617.8200382263486</v>
       </c>
       <c r="U84" s="156" t="n">
-        <v>652.7546812008942</v>
+        <v>652.7546812008941</v>
       </c>
       <c r="V84" s="156" t="n">
-        <v>574.9994744337885</v>
+        <v>574.9994744337884</v>
       </c>
       <c r="W84" s="156" t="n">
-        <v>601.5416093691583</v>
+        <v>601.5416093691581</v>
       </c>
       <c r="X84" s="157" t="n">
         <v>629.2837856924474</v>
       </c>
       <c r="Y84" s="155" t="n">
-        <v>539.3600030310622</v>
+        <v>539.3600030310621</v>
       </c>
       <c r="Z84" s="156" t="n">
-        <v>574.2400056687869</v>
+        <v>574.2400056687868</v>
       </c>
       <c r="AA84" s="156" t="n">
-        <v>506.7514914907653</v>
+        <v>506.7514914907652</v>
       </c>
       <c r="AB84" s="156" t="n">
-        <v>534.0911908470569</v>
+        <v>534.0911908470567</v>
       </c>
       <c r="AC84" s="157" t="n">
-        <v>563.9846142836644</v>
+        <v>563.9846142836643</v>
       </c>
       <c r="AD84" s="158" t="n">
-        <v>7315727.696866723</v>
+        <v>7315727.696866722</v>
       </c>
       <c r="AE84" s="159" t="n">
-        <v>8812640.553662211</v>
+        <v>8812640.553662209</v>
       </c>
       <c r="AF84" s="159" t="n">
-        <v>8819686.481553895</v>
+        <v>8819686.481553894</v>
       </c>
       <c r="AG84" s="159" t="n">
-        <v>10517472.50807059</v>
+        <v>10517472.50807058</v>
       </c>
       <c r="AH84" s="160" t="n">
-        <v>12608434.82853126</v>
+        <v>12608434.82853125</v>
       </c>
     </row>
     <row r="85" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -8872,49 +8872,49 @@
         </is>
       </c>
       <c r="C85" s="179" t="n">
-        <v>652.4276554547382</v>
+        <v>652.4276554547379</v>
       </c>
       <c r="D85" s="180" t="n">
-        <v>713.3982786880795</v>
+        <v>713.3982786880794</v>
       </c>
       <c r="E85" s="180" t="n">
-        <v>717.3309790319878</v>
+        <v>717.3309790319875</v>
       </c>
       <c r="F85" s="180" t="n">
-        <v>767.5527338627652</v>
+        <v>767.552733862765</v>
       </c>
       <c r="G85" s="181" t="n">
-        <v>827.1224262791801</v>
+        <v>827.1224262791799</v>
       </c>
       <c r="H85" s="179" t="n">
-        <v>34.75033347716099</v>
+        <v>34.75033347716097</v>
       </c>
       <c r="I85" s="180" t="n">
-        <v>41.51807913471789</v>
+        <v>41.51807913471788</v>
       </c>
       <c r="J85" s="180" t="n">
-        <v>45.62494429757883</v>
+        <v>45.62494429757881</v>
       </c>
       <c r="K85" s="180" t="n">
-        <v>53.97012389418048</v>
+        <v>53.97012389418047</v>
       </c>
       <c r="L85" s="181" t="n">
-        <v>63.54930287771222</v>
+        <v>63.54930287771221</v>
       </c>
       <c r="M85" s="182" t="n">
-        <v>17794210.45073112</v>
+        <v>17794210.45073111</v>
       </c>
       <c r="N85" s="183" t="n">
         <v>21818734.58795409</v>
       </c>
       <c r="O85" s="183" t="n">
-        <v>24391441.78151438</v>
+        <v>24391441.78151437</v>
       </c>
       <c r="P85" s="183" t="n">
-        <v>29084052.80101772</v>
+        <v>29084052.80101771</v>
       </c>
       <c r="Q85" s="184" t="n">
-        <v>34640551.42056193</v>
+        <v>34640551.42056192</v>
       </c>
       <c r="S85" s="51" t="inlineStr">
         <is>
@@ -8922,49 +8922,49 @@
         </is>
       </c>
       <c r="T85" s="185" t="n">
-        <v>576.3879572371638</v>
+        <v>576.3879572371635</v>
       </c>
       <c r="U85" s="186" t="n">
-        <v>628.8002424909594</v>
+        <v>628.8002424909591</v>
       </c>
       <c r="V85" s="186" t="n">
-        <v>630.3020596717506</v>
+        <v>630.3020596717504</v>
       </c>
       <c r="W85" s="186" t="n">
-        <v>672.1605476888867</v>
+        <v>672.1605476888865</v>
       </c>
       <c r="X85" s="187" t="n">
-        <v>720.2616821398892</v>
+        <v>720.261682139889</v>
       </c>
       <c r="Y85" s="185" t="n">
-        <v>38.48976247850321</v>
+        <v>38.4897624785032</v>
       </c>
       <c r="Z85" s="186" t="n">
-        <v>45.90322937744062</v>
+        <v>45.90322937744061</v>
       </c>
       <c r="AA85" s="186" t="n">
-        <v>50.34060929919262</v>
+        <v>50.3406092991926</v>
       </c>
       <c r="AB85" s="186" t="n">
-        <v>59.40788799443788</v>
+        <v>59.40788799443786</v>
       </c>
       <c r="AC85" s="187" t="n">
-        <v>69.79085107223966</v>
+        <v>69.79085107223965</v>
       </c>
       <c r="AD85" s="188" t="n">
-        <v>17794210.45073112</v>
+        <v>17794210.45073111</v>
       </c>
       <c r="AE85" s="189" t="n">
-        <v>21818734.5879541</v>
+        <v>21818734.58795409</v>
       </c>
       <c r="AF85" s="189" t="n">
-        <v>24391441.78151438</v>
+        <v>24391441.78151437</v>
       </c>
       <c r="AG85" s="189" t="n">
-        <v>29084052.80101772</v>
+        <v>29084052.80101771</v>
       </c>
       <c r="AH85" s="190" t="n">
-        <v>34640551.42056193</v>
+        <v>34640551.42056192</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" thickBot="1"/>
@@ -9898,7 +9898,7 @@
         <v>1571.638735760075</v>
       </c>
       <c r="M95" s="79" t="n">
-        <v>8704.751040581632</v>
+        <v>8704.751040581634</v>
       </c>
       <c r="N95" s="80" t="n">
         <v>9844.740857351189</v>
@@ -9948,7 +9948,7 @@
         <v>2319.824070106877</v>
       </c>
       <c r="AD95" s="79" t="n">
-        <v>13563.71932615367</v>
+        <v>13563.71932615368</v>
       </c>
       <c r="AE95" s="80" t="n">
         <v>15346.61546855934</v>
@@ -9994,7 +9994,7 @@
         <v>30584.22656707017</v>
       </c>
       <c r="E96" s="133" t="n">
-        <v>34003.05088514335</v>
+        <v>34003.05088514336</v>
       </c>
       <c r="F96" s="133" t="n">
         <v>37891.92783491252</v>
